--- a/internal_doc/03.开发设计/兼容MongoDB的关键标记和关键消息.xlsx
+++ b/internal_doc/03.开发设计/兼容MongoDB的关键标记和关键消息.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="469" uniqueCount="209">
   <si>
     <t>MongoDB 驱动与 SequoiaDB对接</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -340,28 +340,10 @@
     <t>FLG_DELETE_RETURNNUM</t>
   </si>
   <si>
-    <t>FLG_QUERY_STRINGOUT</t>
-  </si>
-  <si>
     <t>MsgOpQuery::flags</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>FLG_QUERY_SLAVEOK</t>
-  </si>
-  <si>
-    <t>FLG_QUERY_OPLOGREPLAY</t>
-  </si>
-  <si>
-    <t>FLG_QUERY_NOCONTEXTTIMEOUT</t>
-  </si>
-  <si>
-    <t>FLG_QUERY_AWAITDATA</t>
-  </si>
-  <si>
-    <t>FLG_QUERY_PARTIALREAD</t>
-  </si>
-  <si>
     <t>PREFER_REPL_MASTER</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -437,10 +419,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>distinct</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>用于Query类的flag</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -599,27 +577,15 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>killAllCursors</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>reversed flags ( 4 )</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>cursor ids ( 8 )</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>number( 4 )</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>num Contexts ( 4 )</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>contextIDs ( 8 )</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -727,18 +693,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>auth</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>{ "authenticate": 1, "nonce":xxxx, "user":username, "key":xxxxxxxxx }</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>{ "User": username, "Passwd":xxxxxxx}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>count</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -779,18 +733,10 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>{ "distinct": "mstest", "key":"xxx", "query":{ … } }</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>createIndexes</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>无</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>"$create Index"</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -808,10 +754,6 @@
   </si>
   <si>
     <t xml:space="preserve"> {"Collection": csname.clname, "Index": { "" : name } }</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>{ "dropIndexes": "mstest", "index":"index_name"}</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -882,18 +824,10 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>ns string</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>ns string +  ".system.indexes"</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> { "create": ns, "size": 2^n, "capped":1, "max": 2^30 }</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>兼容mongodb驱动需要讨论的问题：</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -923,6 +857,66 @@
   </si>
   <si>
     <t>左侧是mongodb的消息结构，右侧是sequoiadb的消息结构。相同颜色是消息转换的对应字段。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>FLG_DELETE_SINGLEREMOVE</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>FLG_QUERY_STRINGOUT</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>FLG_QUERY_SLAVEOK</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>FLG_QUERY_OPLOGREPLAY</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>FLG_QUERY_NOCONTEXTTIMEOUT</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>FLG_QUERY_AWAITDATA</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>FLG_QUERY_PARTIALREAD</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>killCursors</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>contextIDs ( 8 * numContext )</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>cursor ids ( 8  * number )</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> { "create": ns name, "size": 2^n, "capped":1, "max": 2^30 }</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>dbname</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{ "deleteIndexes": "clname", "index":"index_name"}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>reservedflags ( 4 )</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>db string db.$cmd</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -984,7 +978,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="18">
+  <fills count="19">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1083,6 +1077,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="3" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1255,15 +1255,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color rgb="FF000000"/>
       </left>
@@ -1389,12 +1380,8 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
+      <left/>
+      <right/>
       <top style="medium">
         <color indexed="64"/>
       </top>
@@ -1404,14 +1391,12 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
+      <left style="medium">
+        <color rgb="FF000000"/>
       </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
+      <right/>
       <top style="medium">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom style="medium">
         <color indexed="64"/>
@@ -1419,14 +1404,23 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
         <color indexed="64"/>
-      </left>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="medium">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </right>
       <top style="medium">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom style="medium">
         <color indexed="64"/>
@@ -1440,7 +1434,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="84">
+  <cellXfs count="92">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1466,13 +1460,13 @@
     <xf numFmtId="0" fontId="5" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="13" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="13" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1506,6 +1500,9 @@
     <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1515,24 +1512,123 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="12" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1542,151 +1638,73 @@
     <xf numFmtId="0" fontId="5" fillId="12" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="13" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="13" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2004,27 +2022,27 @@
   <sheetData>
     <row r="1" spans="1:6" ht="24" customHeight="1">
       <c r="A1" s="22" t="s">
-        <v>204</v>
+        <v>186</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="23.25" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>209</v>
+        <v>191</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="2" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="27.75" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>210</v>
+        <v>192</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -2052,7 +2070,7 @@
         <v>41</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>206</v>
+        <v>188</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="31.5" customHeight="1">
@@ -2081,7 +2099,7 @@
       <c r="D13" s="1"/>
     </row>
     <row r="14" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A14" s="23"/>
+      <c r="A14" s="24"/>
       <c r="B14" s="4" t="s">
         <v>1</v>
       </c>
@@ -2092,14 +2110,14 @@
         <v>55</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>65</v>
+        <v>194</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="25"/>
+      <c r="A15" s="26"/>
       <c r="B15" s="4" t="s">
         <v>2</v>
       </c>
@@ -2119,7 +2137,7 @@
       <c r="D16" s="1"/>
     </row>
     <row r="17" spans="1:6">
-      <c r="A17" s="23" t="s">
+      <c r="A17" s="24" t="s">
         <v>17</v>
       </c>
       <c r="B17" s="4" t="s">
@@ -2139,7 +2157,7 @@
       </c>
     </row>
     <row r="18" spans="1:6">
-      <c r="A18" s="24"/>
+      <c r="A18" s="25"/>
       <c r="B18" s="4" t="s">
         <v>5</v>
       </c>
@@ -2154,7 +2172,7 @@
       </c>
     </row>
     <row r="19" spans="1:6">
-      <c r="A19" s="25"/>
+      <c r="A19" s="26"/>
       <c r="B19" s="4" t="s">
         <v>6</v>
       </c>
@@ -2174,7 +2192,7 @@
       <c r="D20" s="1"/>
     </row>
     <row r="21" spans="1:6">
-      <c r="A21" s="23" t="s">
+      <c r="A21" s="24" t="s">
         <v>16</v>
       </c>
       <c r="B21" s="4" t="s">
@@ -2186,15 +2204,15 @@
       <c r="D21" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="E21" s="1" t="s">
+      <c r="E21" s="23" t="s">
+        <v>195</v>
+      </c>
+      <c r="F21" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="F21" s="1" t="s">
-        <v>71</v>
-      </c>
     </row>
     <row r="22" spans="1:6">
-      <c r="A22" s="24"/>
+      <c r="A22" s="25"/>
       <c r="B22" s="4" t="s">
         <v>8</v>
       </c>
@@ -2205,11 +2223,11 @@
         <v>44</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>72</v>
+        <v>196</v>
       </c>
     </row>
     <row r="23" spans="1:6">
-      <c r="A23" s="24"/>
+      <c r="A23" s="25"/>
       <c r="B23" s="4" t="s">
         <v>10</v>
       </c>
@@ -2218,11 +2236,11 @@
       </c>
       <c r="D23" s="1"/>
       <c r="E23" s="1" t="s">
-        <v>73</v>
+        <v>197</v>
       </c>
     </row>
     <row r="24" spans="1:6">
-      <c r="A24" s="24"/>
+      <c r="A24" s="25"/>
       <c r="B24" s="4" t="s">
         <v>9</v>
       </c>
@@ -2231,11 +2249,11 @@
       </c>
       <c r="D24" s="1"/>
       <c r="E24" s="1" t="s">
-        <v>74</v>
+        <v>198</v>
       </c>
     </row>
     <row r="25" spans="1:6">
-      <c r="A25" s="24"/>
+      <c r="A25" s="25"/>
       <c r="B25" s="4" t="s">
         <v>11</v>
       </c>
@@ -2246,11 +2264,11 @@
         <v>45</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>75</v>
+        <v>199</v>
       </c>
     </row>
     <row r="26" spans="1:6">
-      <c r="A26" s="24"/>
+      <c r="A26" s="25"/>
       <c r="B26" s="4" t="s">
         <v>12</v>
       </c>
@@ -2260,7 +2278,7 @@
       <c r="D26" s="1"/>
     </row>
     <row r="27" spans="1:6">
-      <c r="A27" s="24"/>
+      <c r="A27" s="25"/>
       <c r="B27" s="4" t="s">
         <v>13</v>
       </c>
@@ -2271,11 +2289,11 @@
         <v>58</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>76</v>
+        <v>200</v>
       </c>
     </row>
     <row r="28" spans="1:6">
-      <c r="A28" s="25"/>
+      <c r="A28" s="26"/>
       <c r="B28" s="4" t="s">
         <v>14</v>
       </c>
@@ -2284,6 +2302,9 @@
       </c>
       <c r="D28" s="5" t="s">
         <v>60</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -2311,7 +2332,7 @@
       <c r="D31" s="1"/>
     </row>
     <row r="32" spans="1:6">
-      <c r="A32" s="23" t="s">
+      <c r="A32" s="24" t="s">
         <v>20</v>
       </c>
       <c r="B32" s="4" t="s">
@@ -2325,7 +2346,7 @@
       </c>
     </row>
     <row r="33" spans="1:6">
-      <c r="A33" s="25"/>
+      <c r="A33" s="26"/>
       <c r="B33" s="4" t="s">
         <v>22</v>
       </c>
@@ -2342,7 +2363,7 @@
       <c r="D34" s="1"/>
     </row>
     <row r="35" spans="1:6">
-      <c r="A35" s="26" t="s">
+      <c r="A35" s="27" t="s">
         <v>23</v>
       </c>
       <c r="B35" s="4" t="s">
@@ -2355,14 +2376,14 @@
         <v>50</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
     </row>
     <row r="36" spans="1:6">
-      <c r="A36" s="27"/>
+      <c r="A36" s="28"/>
       <c r="B36" s="4" t="s">
         <v>25</v>
       </c>
@@ -2374,7 +2395,7 @@
       </c>
     </row>
     <row r="37" spans="1:6">
-      <c r="A37" s="27"/>
+      <c r="A37" s="28"/>
       <c r="B37" s="4" t="s">
         <v>26</v>
       </c>
@@ -2385,11 +2406,11 @@
         <v>48</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
     </row>
     <row r="38" spans="1:6">
-      <c r="A38" s="27"/>
+      <c r="A38" s="28"/>
       <c r="B38" s="4" t="s">
         <v>27</v>
       </c>
@@ -2400,11 +2421,11 @@
         <v>47</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
     </row>
     <row r="39" spans="1:6">
-      <c r="A39" s="28"/>
+      <c r="A39" s="29"/>
       <c r="B39" s="4" t="s">
         <v>28</v>
       </c>
@@ -2415,13 +2436,13 @@
         <v>46</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
     </row>
     <row r="40" spans="1:6">
       <c r="A40"/>
       <c r="B40" s="20" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
     </row>
     <row r="41" spans="1:6">
@@ -2432,15 +2453,15 @@
     </row>
     <row r="46" spans="1:6" ht="39.75" customHeight="1">
       <c r="A46" s="1" t="s">
-        <v>208</v>
+        <v>190</v>
       </c>
     </row>
     <row r="47" spans="1:6">
       <c r="A47" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="B47" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
     </row>
     <row r="48" spans="1:6">
@@ -2448,50 +2469,50 @@
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
+        <v>78</v>
+      </c>
+      <c r="B49" t="s">
         <v>84</v>
-      </c>
-      <c r="B49" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="B50" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B51" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="B52" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="B53" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="B54" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -2516,7 +2537,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M203"/>
+  <dimension ref="A1:M183"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="34.25" customWidth="1"/>
@@ -2529,720 +2550,699 @@
   <sheetData>
     <row r="1" spans="1:9" ht="52.5" customHeight="1">
       <c r="A1" t="s">
-        <v>211</v>
+        <v>193</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="63" customHeight="1" thickBot="1">
       <c r="A2" s="1" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="42.75" customHeight="1" thickBot="1">
       <c r="A3" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="B3" s="35" t="s">
-        <v>100</v>
-      </c>
-      <c r="C3" s="36"/>
-      <c r="D3" s="37"/>
+        <v>92</v>
+      </c>
+      <c r="B3" s="54" t="s">
+        <v>93</v>
+      </c>
+      <c r="C3" s="55"/>
+      <c r="D3" s="56"/>
       <c r="G3" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="H3" s="47" t="s">
-        <v>109</v>
-      </c>
-      <c r="I3" s="48"/>
+        <v>101</v>
+      </c>
+      <c r="H3" s="69" t="s">
+        <v>102</v>
+      </c>
+      <c r="I3" s="70"/>
     </row>
     <row r="4" spans="1:9" ht="36" customHeight="1" thickBot="1">
       <c r="A4" s="11" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="C4" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="G4" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="H4" s="71"/>
+      <c r="I4" s="72"/>
+    </row>
+    <row r="5" spans="1:9" ht="33.75" customHeight="1" thickBot="1">
+      <c r="A5" s="43" t="s">
+        <v>98</v>
+      </c>
+      <c r="B5" s="43"/>
+      <c r="C5" s="43"/>
+      <c r="D5" s="43"/>
+      <c r="G5" s="73" t="s">
         <v>104</v>
       </c>
-      <c r="G4" s="13" t="s">
-        <v>110</v>
-      </c>
-      <c r="H4" s="49"/>
-      <c r="I4" s="50"/>
-    </row>
-    <row r="5" spans="1:9" ht="33.75" customHeight="1" thickBot="1">
-      <c r="A5" s="44" t="s">
+      <c r="H5" s="74"/>
+      <c r="I5" s="75"/>
+    </row>
+    <row r="6" spans="1:9" ht="39.75" customHeight="1" thickBot="1">
+      <c r="A6" s="31" t="s">
+        <v>99</v>
+      </c>
+      <c r="B6" s="31"/>
+      <c r="C6" s="31"/>
+      <c r="D6" s="31"/>
+      <c r="G6" s="54" t="s">
         <v>105</v>
       </c>
-      <c r="B5" s="44"/>
-      <c r="C5" s="44"/>
-      <c r="D5" s="44"/>
-      <c r="G5" s="51" t="s">
-        <v>111</v>
-      </c>
-      <c r="H5" s="52"/>
-      <c r="I5" s="53"/>
-    </row>
-    <row r="6" spans="1:9" ht="39.75" customHeight="1" thickBot="1">
-      <c r="A6" s="45" t="s">
-        <v>106</v>
-      </c>
-      <c r="B6" s="45"/>
-      <c r="C6" s="45"/>
-      <c r="D6" s="45"/>
-      <c r="G6" s="35" t="s">
-        <v>112</v>
-      </c>
-      <c r="H6" s="36"/>
-      <c r="I6" s="37"/>
+      <c r="H6" s="55"/>
+      <c r="I6" s="56"/>
     </row>
     <row r="7" spans="1:9" ht="45.75" customHeight="1" thickBot="1">
       <c r="A7" s="46" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="B7" s="46"/>
       <c r="C7" s="46"/>
       <c r="D7" s="46"/>
       <c r="G7" s="13" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="H7" s="12" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="I7" s="12" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="27" customHeight="1" thickBot="1">
       <c r="G8" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="H8" s="29" t="s">
-        <v>135</v>
-      </c>
-      <c r="I8" s="30"/>
+        <v>109</v>
+      </c>
+      <c r="H8" s="63" t="s">
+        <v>128</v>
+      </c>
+      <c r="I8" s="65"/>
     </row>
     <row r="9" spans="1:9" ht="28.5" customHeight="1" thickBot="1">
-      <c r="G9" s="29" t="s">
-        <v>117</v>
-      </c>
-      <c r="H9" s="31"/>
-      <c r="I9" s="30"/>
+      <c r="G9" s="63" t="s">
+        <v>110</v>
+      </c>
+      <c r="H9" s="64"/>
+      <c r="I9" s="65"/>
     </row>
     <row r="10" spans="1:9" ht="30" customHeight="1" thickBot="1">
-      <c r="G10" s="32" t="s">
-        <v>107</v>
-      </c>
-      <c r="H10" s="33"/>
-      <c r="I10" s="34"/>
+      <c r="G10" s="66" t="s">
+        <v>100</v>
+      </c>
+      <c r="H10" s="67"/>
+      <c r="I10" s="68"/>
     </row>
     <row r="13" spans="1:9" ht="55.5" customHeight="1" thickBot="1">
       <c r="A13" s="1" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="45.75" customHeight="1" thickBot="1">
       <c r="A14" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="B14" s="35" t="s">
-        <v>100</v>
-      </c>
-      <c r="C14" s="36"/>
-      <c r="D14" s="37"/>
+        <v>92</v>
+      </c>
+      <c r="B14" s="54" t="s">
+        <v>93</v>
+      </c>
+      <c r="C14" s="55"/>
+      <c r="D14" s="56"/>
       <c r="G14" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="H14" s="47" t="s">
-        <v>109</v>
-      </c>
-      <c r="I14" s="48"/>
+        <v>101</v>
+      </c>
+      <c r="H14" s="69" t="s">
+        <v>102</v>
+      </c>
+      <c r="I14" s="70"/>
     </row>
     <row r="15" spans="1:9" ht="35.25" customHeight="1" thickBot="1">
       <c r="A15" s="11" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="C15" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="G15" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="D15" s="10" t="s">
+      <c r="H15" s="71"/>
+      <c r="I15" s="72"/>
+    </row>
+    <row r="16" spans="1:9" ht="28.5" customHeight="1" thickBot="1">
+      <c r="A16" s="59" t="s">
+        <v>130</v>
+      </c>
+      <c r="B16" s="60"/>
+      <c r="C16" s="60"/>
+      <c r="D16" s="61"/>
+      <c r="G16" s="73" t="s">
         <v>104</v>
       </c>
-      <c r="G15" s="13" t="s">
+      <c r="H16" s="74"/>
+      <c r="I16" s="75"/>
+    </row>
+    <row r="17" spans="1:9" ht="36" customHeight="1" thickBot="1">
+      <c r="A17" s="32" t="s">
+        <v>99</v>
+      </c>
+      <c r="B17" s="33"/>
+      <c r="C17" s="33"/>
+      <c r="D17" s="34"/>
+      <c r="G17" s="54" t="s">
+        <v>105</v>
+      </c>
+      <c r="H17" s="55"/>
+      <c r="I17" s="56"/>
+    </row>
+    <row r="18" spans="1:9" ht="36" customHeight="1" thickBot="1">
+      <c r="A18" s="76" t="s">
+        <v>116</v>
+      </c>
+      <c r="B18" s="76"/>
+      <c r="C18" s="76"/>
+      <c r="D18" s="77"/>
+      <c r="G18" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="H18" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="I18" s="12" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="29.25" customHeight="1" thickBot="1">
+      <c r="A19" s="35" t="s">
+        <v>113</v>
+      </c>
+      <c r="B19" s="36"/>
+      <c r="C19" s="36"/>
+      <c r="D19" s="37"/>
+      <c r="G19" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="H19" s="63" t="s">
+        <v>128</v>
+      </c>
+      <c r="I19" s="65"/>
+    </row>
+    <row r="20" spans="1:9" ht="33" customHeight="1" thickBot="1">
+      <c r="G20" s="63" t="s">
         <v>110</v>
       </c>
-      <c r="H15" s="49"/>
-      <c r="I15" s="50"/>
-    </row>
-    <row r="16" spans="1:9" ht="28.5" customHeight="1" thickBot="1">
-      <c r="A16" s="38" t="s">
-        <v>137</v>
-      </c>
-      <c r="B16" s="39"/>
-      <c r="C16" s="39"/>
-      <c r="D16" s="40"/>
-      <c r="G16" s="51" t="s">
+      <c r="H20" s="64"/>
+      <c r="I20" s="65"/>
+    </row>
+    <row r="21" spans="1:9" ht="33.75" customHeight="1" thickBot="1">
+      <c r="G21" s="66" t="s">
         <v>111</v>
       </c>
-      <c r="H16" s="52"/>
-      <c r="I16" s="53"/>
-    </row>
-    <row r="17" spans="1:9" ht="36" customHeight="1" thickBot="1">
-      <c r="A17" s="41" t="s">
-        <v>106</v>
-      </c>
-      <c r="B17" s="42"/>
-      <c r="C17" s="42"/>
-      <c r="D17" s="43"/>
-      <c r="G17" s="35" t="s">
+      <c r="H21" s="67"/>
+      <c r="I21" s="68"/>
+    </row>
+    <row r="22" spans="1:9" ht="33" customHeight="1" thickBot="1">
+      <c r="G22" s="66" t="s">
         <v>112</v>
       </c>
-      <c r="H17" s="36"/>
-      <c r="I17" s="37"/>
-    </row>
-    <row r="18" spans="1:9" ht="36" customHeight="1" thickBot="1">
-      <c r="A18" s="54" t="s">
-        <v>123</v>
-      </c>
-      <c r="B18" s="54"/>
-      <c r="C18" s="54"/>
-      <c r="D18" s="55"/>
-      <c r="G18" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="H18" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="I18" s="12" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" ht="29.25" customHeight="1" thickBot="1">
-      <c r="A19" s="56" t="s">
-        <v>120</v>
-      </c>
-      <c r="B19" s="57"/>
-      <c r="C19" s="57"/>
-      <c r="D19" s="58"/>
-      <c r="G19" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="H19" s="29" t="s">
-        <v>135</v>
-      </c>
-      <c r="I19" s="30"/>
-    </row>
-    <row r="20" spans="1:9" ht="33" customHeight="1" thickBot="1">
-      <c r="G20" s="29" t="s">
-        <v>117</v>
-      </c>
-      <c r="H20" s="31"/>
-      <c r="I20" s="30"/>
-    </row>
-    <row r="21" spans="1:9" ht="33.75" customHeight="1" thickBot="1">
-      <c r="G21" s="32" t="s">
-        <v>118</v>
-      </c>
-      <c r="H21" s="33"/>
-      <c r="I21" s="34"/>
-    </row>
-    <row r="22" spans="1:9" ht="33" customHeight="1" thickBot="1">
-      <c r="G22" s="32" t="s">
-        <v>119</v>
-      </c>
-      <c r="H22" s="33"/>
-      <c r="I22" s="34"/>
+      <c r="H22" s="67"/>
+      <c r="I22" s="68"/>
     </row>
     <row r="24" spans="1:9" ht="66.75" customHeight="1" thickBot="1">
       <c r="A24" s="1" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="45" customHeight="1" thickBot="1">
       <c r="A25" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="B25" s="35" t="s">
-        <v>100</v>
-      </c>
-      <c r="C25" s="36"/>
-      <c r="D25" s="37"/>
+        <v>92</v>
+      </c>
+      <c r="B25" s="54" t="s">
+        <v>93</v>
+      </c>
+      <c r="C25" s="55"/>
+      <c r="D25" s="56"/>
       <c r="G25" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="H25" s="47" t="s">
-        <v>109</v>
-      </c>
-      <c r="I25" s="48"/>
+        <v>101</v>
+      </c>
+      <c r="H25" s="69" t="s">
+        <v>102</v>
+      </c>
+      <c r="I25" s="70"/>
     </row>
     <row r="26" spans="1:9" ht="40.5" customHeight="1" thickBot="1">
       <c r="A26" s="11" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="C26" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="D26" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="G26" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="D26" s="10" t="s">
+      <c r="H26" s="71"/>
+      <c r="I26" s="72"/>
+    </row>
+    <row r="27" spans="1:9" ht="33" customHeight="1" thickBot="1">
+      <c r="A27" s="59" t="s">
+        <v>130</v>
+      </c>
+      <c r="B27" s="60"/>
+      <c r="C27" s="60"/>
+      <c r="D27" s="61"/>
+      <c r="G27" s="73" t="s">
         <v>104</v>
       </c>
-      <c r="G26" s="13" t="s">
+      <c r="H27" s="74"/>
+      <c r="I27" s="75"/>
+    </row>
+    <row r="28" spans="1:9" ht="30" customHeight="1" thickBot="1">
+      <c r="A28" s="32" t="s">
+        <v>99</v>
+      </c>
+      <c r="B28" s="33"/>
+      <c r="C28" s="33"/>
+      <c r="D28" s="34"/>
+      <c r="G28" s="54" t="s">
+        <v>105</v>
+      </c>
+      <c r="H28" s="55"/>
+      <c r="I28" s="56"/>
+    </row>
+    <row r="29" spans="1:9" ht="30" customHeight="1" thickBot="1">
+      <c r="A29" s="76" t="s">
+        <v>117</v>
+      </c>
+      <c r="B29" s="76"/>
+      <c r="C29" s="76"/>
+      <c r="D29" s="77"/>
+      <c r="G29" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="H29" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="I29" s="12" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="33" customHeight="1" thickBot="1">
+      <c r="A30" s="35" t="s">
+        <v>113</v>
+      </c>
+      <c r="B30" s="36"/>
+      <c r="C30" s="36"/>
+      <c r="D30" s="37"/>
+      <c r="G30" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="H30" s="63" t="s">
+        <v>128</v>
+      </c>
+      <c r="I30" s="65"/>
+    </row>
+    <row r="31" spans="1:9" ht="27.75" customHeight="1" thickBot="1">
+      <c r="G31" s="63" t="s">
         <v>110</v>
       </c>
-      <c r="H26" s="49"/>
-      <c r="I26" s="50"/>
-    </row>
-    <row r="27" spans="1:9" ht="33" customHeight="1" thickBot="1">
-      <c r="A27" s="38" t="s">
-        <v>137</v>
-      </c>
-      <c r="B27" s="39"/>
-      <c r="C27" s="39"/>
-      <c r="D27" s="40"/>
-      <c r="G27" s="51" t="s">
-        <v>111</v>
-      </c>
-      <c r="H27" s="52"/>
-      <c r="I27" s="53"/>
-    </row>
-    <row r="28" spans="1:9" ht="30" customHeight="1" thickBot="1">
-      <c r="A28" s="41" t="s">
-        <v>106</v>
-      </c>
-      <c r="B28" s="42"/>
-      <c r="C28" s="42"/>
-      <c r="D28" s="43"/>
-      <c r="G28" s="35" t="s">
+      <c r="H31" s="64"/>
+      <c r="I31" s="65"/>
+    </row>
+    <row r="32" spans="1:9" ht="33" customHeight="1" thickBot="1">
+      <c r="G32" s="66" t="s">
+        <v>114</v>
+      </c>
+      <c r="H32" s="67"/>
+      <c r="I32" s="68"/>
+    </row>
+    <row r="33" spans="1:9" ht="33" customHeight="1" thickBot="1">
+      <c r="G33" s="66" t="s">
+        <v>115</v>
+      </c>
+      <c r="H33" s="67"/>
+      <c r="I33" s="68"/>
+    </row>
+    <row r="34" spans="1:9" ht="32.25" customHeight="1" thickBot="1">
+      <c r="G34" s="66" t="s">
         <v>112</v>
       </c>
-      <c r="H28" s="36"/>
-      <c r="I28" s="37"/>
-    </row>
-    <row r="29" spans="1:9" ht="30" customHeight="1" thickBot="1">
-      <c r="A29" s="54" t="s">
-        <v>124</v>
-      </c>
-      <c r="B29" s="54"/>
-      <c r="C29" s="54"/>
-      <c r="D29" s="55"/>
-      <c r="G29" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="H29" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="I29" s="12" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" ht="33" customHeight="1" thickBot="1">
-      <c r="A30" s="56" t="s">
-        <v>120</v>
-      </c>
-      <c r="B30" s="57"/>
-      <c r="C30" s="57"/>
-      <c r="D30" s="58"/>
-      <c r="G30" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="H30" s="29" t="s">
-        <v>135</v>
-      </c>
-      <c r="I30" s="30"/>
-    </row>
-    <row r="31" spans="1:9" ht="27.75" customHeight="1" thickBot="1">
-      <c r="G31" s="29" t="s">
-        <v>117</v>
-      </c>
-      <c r="H31" s="31"/>
-      <c r="I31" s="30"/>
-    </row>
-    <row r="32" spans="1:9" ht="33" customHeight="1" thickBot="1">
-      <c r="G32" s="32" t="s">
-        <v>121</v>
-      </c>
-      <c r="H32" s="33"/>
-      <c r="I32" s="34"/>
-    </row>
-    <row r="33" spans="1:9" ht="33" customHeight="1" thickBot="1">
-      <c r="G33" s="32" t="s">
-        <v>122</v>
-      </c>
-      <c r="H33" s="33"/>
-      <c r="I33" s="34"/>
-    </row>
-    <row r="34" spans="1:9" ht="32.25" customHeight="1" thickBot="1">
-      <c r="G34" s="32" t="s">
-        <v>119</v>
-      </c>
-      <c r="H34" s="33"/>
-      <c r="I34" s="34"/>
+      <c r="H34" s="67"/>
+      <c r="I34" s="68"/>
     </row>
     <row r="36" spans="1:9" ht="53.25" customHeight="1">
       <c r="A36" s="1" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
     </row>
     <row r="37" spans="1:9" ht="42" customHeight="1">
       <c r="A37" s="15" t="s">
-        <v>99</v>
-      </c>
-      <c r="B37" s="69" t="s">
-        <v>100</v>
-      </c>
-      <c r="C37" s="70"/>
-      <c r="D37" s="71"/>
+        <v>92</v>
+      </c>
+      <c r="B37" s="40" t="s">
+        <v>93</v>
+      </c>
+      <c r="C37" s="41"/>
+      <c r="D37" s="42"/>
       <c r="G37" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="H37" s="64" t="s">
-        <v>109</v>
-      </c>
-      <c r="I37" s="64"/>
+        <v>101</v>
+      </c>
+      <c r="H37" s="48" t="s">
+        <v>102</v>
+      </c>
+      <c r="I37" s="48"/>
     </row>
     <row r="38" spans="1:9" ht="39" customHeight="1">
       <c r="A38" s="16" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="B38" s="17" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="C38" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="D38" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="G38" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="D38" s="16" t="s">
+      <c r="H38" s="30"/>
+      <c r="I38" s="30"/>
+    </row>
+    <row r="39" spans="1:9" ht="32.25" customHeight="1">
+      <c r="A39" s="43" t="s">
+        <v>129</v>
+      </c>
+      <c r="B39" s="43"/>
+      <c r="C39" s="43"/>
+      <c r="D39" s="43"/>
+      <c r="G39" s="57" t="s">
         <v>104</v>
       </c>
-      <c r="G38" s="16" t="s">
-        <v>110</v>
-      </c>
-      <c r="H38" s="65"/>
-      <c r="I38" s="65"/>
-    </row>
-    <row r="39" spans="1:9" ht="32.25" customHeight="1">
-      <c r="A39" s="44" t="s">
-        <v>136</v>
-      </c>
-      <c r="B39" s="44"/>
-      <c r="C39" s="44"/>
-      <c r="D39" s="44"/>
-      <c r="G39" s="66" t="s">
-        <v>111</v>
-      </c>
-      <c r="H39" s="66"/>
-      <c r="I39" s="66"/>
+      <c r="H39" s="57"/>
+      <c r="I39" s="57"/>
     </row>
     <row r="40" spans="1:9" ht="24" customHeight="1">
-      <c r="A40" s="45" t="s">
+      <c r="A40" s="31" t="s">
+        <v>99</v>
+      </c>
+      <c r="B40" s="31"/>
+      <c r="C40" s="31"/>
+      <c r="D40" s="31"/>
+      <c r="G40" s="58" t="s">
+        <v>105</v>
+      </c>
+      <c r="H40" s="58"/>
+      <c r="I40" s="58"/>
+    </row>
+    <row r="41" spans="1:9" ht="24" customHeight="1">
+      <c r="A41" s="44" t="s">
+        <v>119</v>
+      </c>
+      <c r="B41" s="44"/>
+      <c r="C41" s="44"/>
+      <c r="D41" s="44"/>
+      <c r="G41" s="16" t="s">
         <v>106</v>
       </c>
-      <c r="B40" s="45"/>
-      <c r="C40" s="45"/>
-      <c r="D40" s="45"/>
-      <c r="G40" s="67" t="s">
-        <v>112</v>
-      </c>
-      <c r="H40" s="67"/>
-      <c r="I40" s="67"/>
-    </row>
-    <row r="41" spans="1:9" ht="24" customHeight="1">
-      <c r="A41" s="59" t="s">
-        <v>126</v>
-      </c>
-      <c r="B41" s="59"/>
-      <c r="C41" s="59"/>
-      <c r="D41" s="59"/>
-      <c r="G41" s="16" t="s">
-        <v>113</v>
-      </c>
       <c r="H41" s="16" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="I41" s="16" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
     </row>
     <row r="42" spans="1:9" ht="24" customHeight="1">
-      <c r="A42" s="60" t="s">
-        <v>127</v>
-      </c>
-      <c r="B42" s="60"/>
-      <c r="C42" s="60"/>
-      <c r="D42" s="60"/>
+      <c r="A42" s="45" t="s">
+        <v>120</v>
+      </c>
+      <c r="B42" s="45"/>
+      <c r="C42" s="45"/>
+      <c r="D42" s="45"/>
       <c r="G42" s="14" t="s">
-        <v>116</v>
-      </c>
-      <c r="H42" s="45" t="s">
-        <v>135</v>
-      </c>
-      <c r="I42" s="45"/>
+        <v>109</v>
+      </c>
+      <c r="H42" s="31" t="s">
+        <v>128</v>
+      </c>
+      <c r="I42" s="31"/>
     </row>
     <row r="43" spans="1:9" ht="24" customHeight="1">
       <c r="A43" s="46" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="B43" s="46"/>
       <c r="C43" s="46"/>
       <c r="D43" s="46"/>
       <c r="G43" s="18" t="s">
-        <v>133</v>
-      </c>
-      <c r="H43" s="62" t="s">
-        <v>134</v>
-      </c>
-      <c r="I43" s="63"/>
+        <v>126</v>
+      </c>
+      <c r="H43" s="38" t="s">
+        <v>127</v>
+      </c>
+      <c r="I43" s="39"/>
     </row>
     <row r="44" spans="1:9" ht="33" customHeight="1">
-      <c r="A44" s="61" t="s">
-        <v>129</v>
-      </c>
-      <c r="B44" s="61"/>
-      <c r="C44" s="61"/>
-      <c r="D44" s="61"/>
-      <c r="G44" s="45" t="s">
-        <v>117</v>
-      </c>
-      <c r="H44" s="45"/>
-      <c r="I44" s="45"/>
+      <c r="A44" s="47" t="s">
+        <v>122</v>
+      </c>
+      <c r="B44" s="47"/>
+      <c r="C44" s="47"/>
+      <c r="D44" s="47"/>
+      <c r="G44" s="31" t="s">
+        <v>110</v>
+      </c>
+      <c r="H44" s="31"/>
+      <c r="I44" s="31"/>
     </row>
     <row r="45" spans="1:9" ht="35.25" customHeight="1">
       <c r="G45" s="46" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="H45" s="46"/>
       <c r="I45" s="46"/>
     </row>
     <row r="46" spans="1:9" ht="30.75" customHeight="1">
-      <c r="G46" s="68" t="s">
-        <v>131</v>
-      </c>
-      <c r="H46" s="68"/>
-      <c r="I46" s="68"/>
+      <c r="G46" s="62" t="s">
+        <v>124</v>
+      </c>
+      <c r="H46" s="62"/>
+      <c r="I46" s="62"/>
     </row>
     <row r="47" spans="1:9" ht="33" customHeight="1">
       <c r="G47" s="46" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="H47" s="46"/>
       <c r="I47" s="46"/>
     </row>
     <row r="48" spans="1:9" ht="31.5" customHeight="1">
       <c r="G48" s="46" t="s">
-        <v>174</v>
+        <v>161</v>
       </c>
       <c r="H48" s="46"/>
       <c r="I48" s="46"/>
     </row>
     <row r="50" spans="1:9" ht="59.25" customHeight="1">
       <c r="A50" s="1" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
     </row>
     <row r="51" spans="1:9" ht="35.25" customHeight="1">
       <c r="A51" s="15" t="s">
-        <v>99</v>
-      </c>
-      <c r="B51" s="69" t="s">
-        <v>100</v>
-      </c>
-      <c r="C51" s="70"/>
-      <c r="D51" s="71"/>
+        <v>92</v>
+      </c>
+      <c r="B51" s="40" t="s">
+        <v>93</v>
+      </c>
+      <c r="C51" s="41"/>
+      <c r="D51" s="42"/>
       <c r="G51" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="H51" s="64" t="s">
-        <v>109</v>
-      </c>
-      <c r="I51" s="64"/>
+        <v>101</v>
+      </c>
+      <c r="H51" s="48" t="s">
+        <v>102</v>
+      </c>
+      <c r="I51" s="48"/>
     </row>
     <row r="52" spans="1:9" ht="33" customHeight="1">
       <c r="A52" s="16" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="B52" s="17" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="C52" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="D52" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="G52" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="D52" s="16" t="s">
+      <c r="H52" s="30"/>
+      <c r="I52" s="30"/>
+    </row>
+    <row r="53" spans="1:9" ht="33" customHeight="1">
+      <c r="A53" s="43" t="s">
+        <v>118</v>
+      </c>
+      <c r="B53" s="43"/>
+      <c r="C53" s="43"/>
+      <c r="D53" s="43"/>
+      <c r="G53" s="57" t="s">
         <v>104</v>
       </c>
-      <c r="G52" s="16" t="s">
-        <v>110</v>
-      </c>
-      <c r="H52" s="65"/>
-      <c r="I52" s="65"/>
-    </row>
-    <row r="53" spans="1:9" ht="33" customHeight="1">
-      <c r="A53" s="44" t="s">
-        <v>125</v>
-      </c>
-      <c r="B53" s="44"/>
-      <c r="C53" s="44"/>
-      <c r="D53" s="44"/>
-      <c r="G53" s="66" t="s">
-        <v>111</v>
-      </c>
-      <c r="H53" s="66"/>
-      <c r="I53" s="66"/>
+      <c r="H53" s="57"/>
+      <c r="I53" s="57"/>
     </row>
     <row r="54" spans="1:9" ht="28.5" customHeight="1">
-      <c r="A54" s="45" t="s">
-        <v>106</v>
-      </c>
-      <c r="B54" s="45"/>
-      <c r="C54" s="45"/>
-      <c r="D54" s="45"/>
-      <c r="G54" s="67" t="s">
-        <v>112</v>
-      </c>
-      <c r="H54" s="67"/>
-      <c r="I54" s="67"/>
+      <c r="A54" s="31" t="s">
+        <v>99</v>
+      </c>
+      <c r="B54" s="31"/>
+      <c r="C54" s="31"/>
+      <c r="D54" s="31"/>
+      <c r="G54" s="58" t="s">
+        <v>105</v>
+      </c>
+      <c r="H54" s="58"/>
+      <c r="I54" s="58"/>
     </row>
     <row r="55" spans="1:9" ht="30" customHeight="1">
-      <c r="A55" s="60" t="s">
-        <v>127</v>
-      </c>
-      <c r="B55" s="60"/>
-      <c r="C55" s="60"/>
-      <c r="D55" s="60"/>
-      <c r="G55" s="16" t="s">
-        <v>113</v>
-      </c>
-      <c r="H55" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="I55" s="16" t="s">
-        <v>115</v>
-      </c>
+      <c r="A55" s="45" t="s">
+        <v>120</v>
+      </c>
+      <c r="B55" s="45"/>
+      <c r="C55" s="45"/>
+      <c r="D55" s="45"/>
+      <c r="G55" s="59" t="s">
+        <v>132</v>
+      </c>
+      <c r="H55" s="60"/>
+      <c r="I55" s="61"/>
     </row>
     <row r="56" spans="1:9" ht="30" customHeight="1">
       <c r="A56" s="46" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="B56" s="46"/>
       <c r="C56" s="46"/>
       <c r="D56" s="46"/>
-      <c r="G56" s="38" t="s">
-        <v>139</v>
-      </c>
-      <c r="H56" s="39"/>
-      <c r="I56" s="40"/>
-    </row>
-    <row r="57" spans="1:9" ht="34.5" customHeight="1">
-      <c r="G57" s="45" t="s">
-        <v>140</v>
-      </c>
-      <c r="H57" s="45"/>
-      <c r="I57" s="45"/>
-    </row>
+      <c r="G56" s="31" t="s">
+        <v>133</v>
+      </c>
+      <c r="H56" s="31"/>
+      <c r="I56" s="31"/>
+    </row>
+    <row r="57" spans="1:9" ht="34.5" customHeight="1"/>
     <row r="59" spans="1:9" ht="37.5" customHeight="1">
       <c r="A59" s="1" t="s">
-        <v>141</v>
-      </c>
+        <v>201</v>
+      </c>
+      <c r="G59" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="H59" s="48" t="s">
+        <v>102</v>
+      </c>
+      <c r="I59" s="48"/>
     </row>
     <row r="60" spans="1:9" ht="31.5" customHeight="1">
       <c r="A60" s="15" t="s">
-        <v>99</v>
-      </c>
-      <c r="B60" s="69" t="s">
-        <v>100</v>
-      </c>
-      <c r="C60" s="70"/>
-      <c r="D60" s="71"/>
-      <c r="G60" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="H60" s="64" t="s">
-        <v>109</v>
-      </c>
-      <c r="I60" s="64"/>
+        <v>92</v>
+      </c>
+      <c r="B60" s="40" t="s">
+        <v>93</v>
+      </c>
+      <c r="C60" s="41"/>
+      <c r="D60" s="42"/>
+      <c r="G60" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="H60" s="30"/>
+      <c r="I60" s="30"/>
     </row>
     <row r="61" spans="1:9" ht="30.75" customHeight="1">
       <c r="A61" s="16" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="B61" s="17" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="C61" s="16" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="D61" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="G61" s="57" t="s">
         <v>104</v>
       </c>
-      <c r="G61" s="16" t="s">
-        <v>110</v>
-      </c>
-      <c r="H61" s="65"/>
-      <c r="I61" s="65"/>
+      <c r="H61" s="57"/>
+      <c r="I61" s="57"/>
     </row>
     <row r="62" spans="1:9" ht="33.75" customHeight="1">
-      <c r="A62" s="44" t="s">
-        <v>142</v>
-      </c>
-      <c r="B62" s="44"/>
-      <c r="C62" s="44"/>
-      <c r="D62" s="44"/>
-      <c r="G62" s="66" t="s">
-        <v>111</v>
-      </c>
-      <c r="H62" s="66"/>
-      <c r="I62" s="66"/>
+      <c r="A62" s="43" t="s">
+        <v>134</v>
+      </c>
+      <c r="B62" s="43"/>
+      <c r="C62" s="43"/>
+      <c r="D62" s="43"/>
+      <c r="G62" s="58" t="s">
+        <v>105</v>
+      </c>
+      <c r="H62" s="58"/>
+      <c r="I62" s="58"/>
     </row>
     <row r="63" spans="1:9" ht="27" customHeight="1">
-      <c r="A63" s="45" t="s">
-        <v>144</v>
-      </c>
-      <c r="B63" s="45"/>
-      <c r="C63" s="45"/>
-      <c r="D63" s="45"/>
-      <c r="G63" s="67" t="s">
-        <v>112</v>
-      </c>
-      <c r="H63" s="67"/>
-      <c r="I63" s="67"/>
+      <c r="A63" s="31" t="s">
+        <v>135</v>
+      </c>
+      <c r="B63" s="31"/>
+      <c r="C63" s="31"/>
+      <c r="D63" s="31"/>
+      <c r="G63" s="31" t="s">
+        <v>136</v>
+      </c>
+      <c r="H63" s="31"/>
+      <c r="I63" s="31"/>
     </row>
     <row r="64" spans="1:9" ht="27.75" customHeight="1">
       <c r="A64" s="46" t="s">
-        <v>143</v>
+        <v>203</v>
       </c>
       <c r="B64" s="46"/>
       <c r="C64" s="46"/>
       <c r="D64" s="46"/>
-      <c r="G64" s="16" t="s">
-        <v>113</v>
-      </c>
-      <c r="H64" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="I64" s="16" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="65" spans="1:13" ht="27.75" customHeight="1">
-      <c r="G65" s="45" t="s">
-        <v>145</v>
-      </c>
-      <c r="H65" s="45"/>
-      <c r="I65" s="45"/>
-    </row>
-    <row r="66" spans="1:13" ht="26.25" customHeight="1">
-      <c r="G66" s="38" t="s">
-        <v>146</v>
-      </c>
-      <c r="H66" s="39"/>
-      <c r="I66" s="40"/>
-    </row>
+      <c r="G64" s="59" t="s">
+        <v>202</v>
+      </c>
+      <c r="H64" s="60"/>
+      <c r="I64" s="61"/>
+    </row>
+    <row r="65" spans="1:13" ht="27.75" customHeight="1"/>
+    <row r="66" spans="1:13" ht="26.25" customHeight="1"/>
     <row r="67" spans="1:13" ht="27.75" customHeight="1"/>
     <row r="68" spans="1:13" ht="54.75" customHeight="1">
       <c r="A68" s="19"/>
@@ -3261,1479 +3261,1177 @@
     </row>
     <row r="69" spans="1:13" ht="85.5" customHeight="1">
       <c r="A69" s="1" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
     </row>
     <row r="71" spans="1:13">
       <c r="A71" s="1" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
     </row>
     <row r="72" spans="1:13" ht="45" customHeight="1">
       <c r="A72" s="15" t="s">
-        <v>99</v>
-      </c>
-      <c r="B72" s="69" t="s">
-        <v>100</v>
-      </c>
-      <c r="C72" s="70"/>
-      <c r="D72" s="71"/>
+        <v>92</v>
+      </c>
+      <c r="B72" s="40" t="s">
+        <v>93</v>
+      </c>
+      <c r="C72" s="41"/>
+      <c r="D72" s="42"/>
       <c r="G72" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="H72" s="64" t="s">
-        <v>109</v>
-      </c>
-      <c r="I72" s="64"/>
+        <v>101</v>
+      </c>
+      <c r="H72" s="48" t="s">
+        <v>102</v>
+      </c>
+      <c r="I72" s="48"/>
     </row>
     <row r="73" spans="1:13" ht="44.25" customHeight="1">
       <c r="A73" s="16" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="B73" s="17" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="C73" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="D73" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="G73" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="D73" s="16" t="s">
+      <c r="H73" s="30"/>
+      <c r="I73" s="30"/>
+    </row>
+    <row r="74" spans="1:13" ht="32.25" customHeight="1">
+      <c r="A74" s="43" t="s">
+        <v>140</v>
+      </c>
+      <c r="B74" s="43"/>
+      <c r="C74" s="43"/>
+      <c r="D74" s="43"/>
+      <c r="G74" s="49" t="s">
         <v>104</v>
       </c>
-      <c r="G73" s="16" t="s">
-        <v>110</v>
-      </c>
-      <c r="H73" s="65"/>
-      <c r="I73" s="65"/>
-    </row>
-    <row r="74" spans="1:13" ht="32.25" customHeight="1">
-      <c r="A74" s="44" t="s">
-        <v>150</v>
-      </c>
-      <c r="B74" s="44"/>
-      <c r="C74" s="44"/>
-      <c r="D74" s="44"/>
-      <c r="G74" s="66" t="s">
-        <v>111</v>
-      </c>
-      <c r="H74" s="66"/>
-      <c r="I74" s="66"/>
+      <c r="H74" s="50"/>
+      <c r="I74" s="51"/>
     </row>
     <row r="75" spans="1:13" ht="30" customHeight="1">
-      <c r="A75" s="45" t="s">
+      <c r="A75" s="31" t="s">
+        <v>139</v>
+      </c>
+      <c r="B75" s="31"/>
+      <c r="C75" s="31"/>
+      <c r="D75" s="31"/>
+      <c r="G75" s="40" t="s">
         <v>149</v>
       </c>
-      <c r="B75" s="45"/>
-      <c r="C75" s="45"/>
-      <c r="D75" s="45"/>
-      <c r="G75" s="67" t="s">
-        <v>159</v>
-      </c>
-      <c r="H75" s="67"/>
-      <c r="I75" s="67"/>
+      <c r="H75" s="41"/>
+      <c r="I75" s="42"/>
     </row>
     <row r="76" spans="1:13" ht="36" customHeight="1">
-      <c r="A76" s="59" t="s">
-        <v>153</v>
-      </c>
-      <c r="B76" s="59"/>
-      <c r="C76" s="59"/>
-      <c r="D76" s="59"/>
+      <c r="A76" s="44" t="s">
+        <v>143</v>
+      </c>
+      <c r="B76" s="44"/>
+      <c r="C76" s="44"/>
+      <c r="D76" s="44"/>
       <c r="G76" s="16" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="H76" s="16" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="I76" s="16" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
     </row>
     <row r="77" spans="1:13" ht="29.25" customHeight="1">
-      <c r="A77" s="60" t="s">
-        <v>152</v>
-      </c>
-      <c r="B77" s="60"/>
-      <c r="C77" s="60"/>
-      <c r="D77" s="60"/>
+      <c r="A77" s="45" t="s">
+        <v>142</v>
+      </c>
+      <c r="B77" s="45"/>
+      <c r="C77" s="45"/>
+      <c r="D77" s="45"/>
       <c r="G77" s="14" t="s">
-        <v>156</v>
-      </c>
-      <c r="H77" s="45" t="s">
-        <v>135</v>
-      </c>
-      <c r="I77" s="45"/>
+        <v>146</v>
+      </c>
+      <c r="H77" s="31" t="s">
+        <v>128</v>
+      </c>
+      <c r="I77" s="31"/>
     </row>
     <row r="78" spans="1:13" ht="29.25" customHeight="1">
       <c r="A78" s="46" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="B78" s="46"/>
       <c r="C78" s="46"/>
       <c r="D78" s="46"/>
       <c r="G78" s="18" t="s">
-        <v>157</v>
-      </c>
-      <c r="H78" s="62" t="s">
-        <v>158</v>
-      </c>
-      <c r="I78" s="63"/>
+        <v>147</v>
+      </c>
+      <c r="H78" s="38" t="s">
+        <v>148</v>
+      </c>
+      <c r="I78" s="39"/>
     </row>
     <row r="79" spans="1:13" ht="28.5" customHeight="1">
-      <c r="A79" s="61" t="s">
-        <v>151</v>
-      </c>
-      <c r="B79" s="61"/>
-      <c r="C79" s="61"/>
-      <c r="D79" s="61"/>
-      <c r="G79" s="45" t="s">
-        <v>199</v>
-      </c>
-      <c r="H79" s="45"/>
-      <c r="I79" s="45"/>
+      <c r="A79" s="47" t="s">
+        <v>141</v>
+      </c>
+      <c r="B79" s="47"/>
+      <c r="C79" s="47"/>
+      <c r="D79" s="47"/>
+      <c r="G79" s="32" t="s">
+        <v>183</v>
+      </c>
+      <c r="H79" s="33"/>
+      <c r="I79" s="34"/>
     </row>
     <row r="80" spans="1:13" ht="14.25">
-      <c r="G80" s="46" t="s">
-        <v>200</v>
-      </c>
-      <c r="H80" s="46"/>
-      <c r="I80" s="46"/>
+      <c r="G80" s="35" t="s">
+        <v>184</v>
+      </c>
+      <c r="H80" s="36"/>
+      <c r="I80" s="37"/>
     </row>
     <row r="85" spans="1:9" ht="49.5" customHeight="1" thickBot="1">
       <c r="A85" s="1" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
     </row>
     <row r="86" spans="1:9" ht="38.25" customHeight="1" thickBot="1">
       <c r="A86" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="B86" s="35" t="s">
-        <v>100</v>
-      </c>
-      <c r="C86" s="36"/>
-      <c r="D86" s="37"/>
+        <v>92</v>
+      </c>
+      <c r="B86" s="54" t="s">
+        <v>93</v>
+      </c>
+      <c r="C86" s="55"/>
+      <c r="D86" s="56"/>
       <c r="G86" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="H86" s="64" t="s">
-        <v>109</v>
-      </c>
-      <c r="I86" s="64"/>
+        <v>101</v>
+      </c>
+      <c r="H86" s="48" t="s">
+        <v>102</v>
+      </c>
+      <c r="I86" s="48"/>
     </row>
     <row r="87" spans="1:9" ht="40.5" customHeight="1">
       <c r="A87" s="11" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="B87" s="9" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="C87" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="D87" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="G87" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="D87" s="10" t="s">
+      <c r="H87" s="30"/>
+      <c r="I87" s="30"/>
+    </row>
+    <row r="88" spans="1:9" ht="48" customHeight="1">
+      <c r="A88" s="43" t="s">
+        <v>207</v>
+      </c>
+      <c r="B88" s="43"/>
+      <c r="C88" s="43"/>
+      <c r="D88" s="43"/>
+      <c r="G88" s="49" t="s">
         <v>104</v>
       </c>
-      <c r="G87" s="16" t="s">
-        <v>110</v>
-      </c>
-      <c r="H87" s="65"/>
-      <c r="I87" s="65"/>
-    </row>
-    <row r="88" spans="1:9" ht="48" customHeight="1">
-      <c r="A88" s="44" t="s">
-        <v>105</v>
-      </c>
-      <c r="B88" s="44"/>
-      <c r="C88" s="44"/>
-      <c r="D88" s="44"/>
-      <c r="G88" s="66" t="s">
-        <v>111</v>
-      </c>
-      <c r="H88" s="66"/>
-      <c r="I88" s="66"/>
+      <c r="H88" s="50"/>
+      <c r="I88" s="51"/>
     </row>
     <row r="89" spans="1:9" ht="35.25" customHeight="1">
-      <c r="A89" s="45" t="s">
-        <v>201</v>
-      </c>
-      <c r="B89" s="45"/>
-      <c r="C89" s="45"/>
-      <c r="D89" s="45"/>
-      <c r="G89" s="67" t="s">
-        <v>159</v>
-      </c>
-      <c r="H89" s="67"/>
-      <c r="I89" s="67"/>
+      <c r="A89" s="31" t="s">
+        <v>208</v>
+      </c>
+      <c r="B89" s="31"/>
+      <c r="C89" s="31"/>
+      <c r="D89" s="31"/>
+      <c r="G89" s="40" t="s">
+        <v>149</v>
+      </c>
+      <c r="H89" s="41"/>
+      <c r="I89" s="42"/>
     </row>
     <row r="90" spans="1:9" ht="37.5" customHeight="1">
       <c r="A90" s="46" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B90" s="46"/>
       <c r="C90" s="46"/>
       <c r="D90" s="46"/>
       <c r="G90" s="16" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="H90" s="16" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="I90" s="16" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
     </row>
     <row r="91" spans="1:9" ht="27.75" customHeight="1">
       <c r="G91" s="14" t="s">
-        <v>156</v>
-      </c>
-      <c r="H91" s="45" t="s">
-        <v>135</v>
-      </c>
-      <c r="I91" s="45"/>
+        <v>146</v>
+      </c>
+      <c r="H91" s="31" t="s">
+        <v>128</v>
+      </c>
+      <c r="I91" s="31"/>
     </row>
     <row r="92" spans="1:9" ht="33.75" customHeight="1">
       <c r="G92" s="18" t="s">
-        <v>157</v>
-      </c>
-      <c r="H92" s="62" t="s">
-        <v>158</v>
-      </c>
-      <c r="I92" s="63"/>
+        <v>147</v>
+      </c>
+      <c r="H92" s="38" t="s">
+        <v>148</v>
+      </c>
+      <c r="I92" s="39"/>
     </row>
     <row r="93" spans="1:9" ht="30.75" customHeight="1">
-      <c r="G93" s="45" t="s">
-        <v>155</v>
-      </c>
-      <c r="H93" s="45"/>
-      <c r="I93" s="45"/>
+      <c r="G93" s="32" t="s">
+        <v>145</v>
+      </c>
+      <c r="H93" s="33"/>
+      <c r="I93" s="34"/>
     </row>
     <row r="94" spans="1:9" ht="36" customHeight="1">
-      <c r="G94" s="46" t="s">
-        <v>164</v>
-      </c>
-      <c r="H94" s="46"/>
-      <c r="I94" s="46"/>
+      <c r="G94" s="35" t="s">
+        <v>154</v>
+      </c>
+      <c r="H94" s="36"/>
+      <c r="I94" s="37"/>
     </row>
     <row r="95" spans="1:9" ht="33.75" customHeight="1"/>
     <row r="96" spans="1:9" ht="33.75" customHeight="1">
       <c r="A96" s="1" t="s">
-        <v>197</v>
+        <v>181</v>
       </c>
     </row>
     <row r="97" spans="1:9" ht="31.5" customHeight="1">
       <c r="A97" s="15" t="s">
-        <v>99</v>
-      </c>
-      <c r="B97" s="69" t="s">
-        <v>100</v>
-      </c>
-      <c r="C97" s="70"/>
-      <c r="D97" s="71"/>
+        <v>92</v>
+      </c>
+      <c r="B97" s="40" t="s">
+        <v>93</v>
+      </c>
+      <c r="C97" s="41"/>
+      <c r="D97" s="42"/>
       <c r="G97" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="H97" s="64" t="s">
-        <v>109</v>
-      </c>
-      <c r="I97" s="64"/>
+        <v>101</v>
+      </c>
+      <c r="H97" s="48" t="s">
+        <v>102</v>
+      </c>
+      <c r="I97" s="48"/>
     </row>
     <row r="98" spans="1:9" ht="28.5">
       <c r="A98" s="16" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="B98" s="17" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="C98" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="D98" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="G98" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="D98" s="16" t="s">
+      <c r="H98" s="30"/>
+      <c r="I98" s="30"/>
+    </row>
+    <row r="99" spans="1:9" ht="36.75" customHeight="1">
+      <c r="A99" s="43" t="s">
+        <v>140</v>
+      </c>
+      <c r="B99" s="43"/>
+      <c r="C99" s="43"/>
+      <c r="D99" s="43"/>
+      <c r="G99" s="49" t="s">
         <v>104</v>
       </c>
-      <c r="G98" s="16" t="s">
-        <v>110</v>
-      </c>
-      <c r="H98" s="65"/>
-      <c r="I98" s="65"/>
-    </row>
-    <row r="99" spans="1:9" ht="36.75" customHeight="1">
-      <c r="A99" s="44" t="s">
-        <v>150</v>
-      </c>
-      <c r="B99" s="44"/>
-      <c r="C99" s="44"/>
-      <c r="D99" s="44"/>
-      <c r="G99" s="66" t="s">
-        <v>111</v>
-      </c>
-      <c r="H99" s="66"/>
-      <c r="I99" s="66"/>
+      <c r="H99" s="50"/>
+      <c r="I99" s="51"/>
     </row>
     <row r="100" spans="1:9" ht="30.75" customHeight="1">
-      <c r="A100" s="45" t="s">
+      <c r="A100" s="31" t="s">
+        <v>139</v>
+      </c>
+      <c r="B100" s="31"/>
+      <c r="C100" s="31"/>
+      <c r="D100" s="31"/>
+      <c r="G100" s="40" t="s">
         <v>149</v>
       </c>
-      <c r="B100" s="45"/>
-      <c r="C100" s="45"/>
-      <c r="D100" s="45"/>
-      <c r="G100" s="67" t="s">
-        <v>159</v>
-      </c>
-      <c r="H100" s="67"/>
-      <c r="I100" s="67"/>
+      <c r="H100" s="41"/>
+      <c r="I100" s="42"/>
     </row>
     <row r="101" spans="1:9" ht="27.75" customHeight="1">
-      <c r="A101" s="59" t="s">
-        <v>153</v>
-      </c>
-      <c r="B101" s="59"/>
-      <c r="C101" s="59"/>
-      <c r="D101" s="59"/>
+      <c r="A101" s="44" t="s">
+        <v>143</v>
+      </c>
+      <c r="B101" s="44"/>
+      <c r="C101" s="44"/>
+      <c r="D101" s="44"/>
       <c r="G101" s="16" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="H101" s="16" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="I101" s="16" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
     </row>
     <row r="102" spans="1:9" ht="30" customHeight="1">
-      <c r="A102" s="60" t="s">
-        <v>152</v>
-      </c>
-      <c r="B102" s="60"/>
-      <c r="C102" s="60"/>
-      <c r="D102" s="60"/>
+      <c r="A102" s="45" t="s">
+        <v>142</v>
+      </c>
+      <c r="B102" s="45"/>
+      <c r="C102" s="45"/>
+      <c r="D102" s="45"/>
       <c r="G102" s="14" t="s">
-        <v>156</v>
-      </c>
-      <c r="H102" s="45" t="s">
-        <v>135</v>
-      </c>
-      <c r="I102" s="45"/>
+        <v>146</v>
+      </c>
+      <c r="H102" s="31" t="s">
+        <v>128</v>
+      </c>
+      <c r="I102" s="31"/>
     </row>
     <row r="103" spans="1:9" ht="27.75" customHeight="1">
       <c r="A103" s="46" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
       <c r="B103" s="46"/>
       <c r="C103" s="46"/>
       <c r="D103" s="46"/>
       <c r="G103" s="18" t="s">
+        <v>147</v>
+      </c>
+      <c r="H103" s="38" t="s">
+        <v>148</v>
+      </c>
+      <c r="I103" s="39"/>
+    </row>
+    <row r="104" spans="1:9" ht="39" customHeight="1">
+      <c r="A104" s="47" t="s">
+        <v>141</v>
+      </c>
+      <c r="B104" s="47"/>
+      <c r="C104" s="47"/>
+      <c r="D104" s="47"/>
+      <c r="G104" s="32" t="s">
+        <v>152</v>
+      </c>
+      <c r="H104" s="33"/>
+      <c r="I104" s="34"/>
+    </row>
+    <row r="105" spans="1:9" ht="30.75" customHeight="1">
+      <c r="G105" s="35" t="s">
+        <v>153</v>
+      </c>
+      <c r="H105" s="36"/>
+      <c r="I105" s="37"/>
+    </row>
+    <row r="111" spans="1:9" ht="52.5" customHeight="1">
+      <c r="A111" s="1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9" ht="37.5" customHeight="1">
+      <c r="A112" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="B112" s="40" t="s">
+        <v>93</v>
+      </c>
+      <c r="C112" s="41"/>
+      <c r="D112" s="42"/>
+      <c r="G112" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="H112" s="48" t="s">
+        <v>102</v>
+      </c>
+      <c r="I112" s="48"/>
+    </row>
+    <row r="113" spans="1:9" ht="35.25" customHeight="1">
+      <c r="A113" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="B113" s="17" t="s">
+        <v>144</v>
+      </c>
+      <c r="C113" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="D113" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="G113" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="H113" s="30"/>
+      <c r="I113" s="30"/>
+    </row>
+    <row r="114" spans="1:9" ht="31.5" customHeight="1">
+      <c r="A114" s="43" t="s">
+        <v>140</v>
+      </c>
+      <c r="B114" s="43"/>
+      <c r="C114" s="43"/>
+      <c r="D114" s="43"/>
+      <c r="G114" s="49" t="s">
+        <v>104</v>
+      </c>
+      <c r="H114" s="50"/>
+      <c r="I114" s="51"/>
+    </row>
+    <row r="115" spans="1:9" ht="32.25" customHeight="1">
+      <c r="A115" s="31" t="s">
+        <v>139</v>
+      </c>
+      <c r="B115" s="31"/>
+      <c r="C115" s="31"/>
+      <c r="D115" s="31"/>
+      <c r="G115" s="40" t="s">
+        <v>149</v>
+      </c>
+      <c r="H115" s="41"/>
+      <c r="I115" s="42"/>
+    </row>
+    <row r="116" spans="1:9" ht="29.25" customHeight="1">
+      <c r="A116" s="44" t="s">
+        <v>143</v>
+      </c>
+      <c r="B116" s="44"/>
+      <c r="C116" s="44"/>
+      <c r="D116" s="44"/>
+      <c r="G116" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="H116" s="16" t="s">
+        <v>107</v>
+      </c>
+      <c r="I116" s="16" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9" ht="27.75" customHeight="1">
+      <c r="A117" s="45" t="s">
+        <v>142</v>
+      </c>
+      <c r="B117" s="45"/>
+      <c r="C117" s="45"/>
+      <c r="D117" s="45"/>
+      <c r="G117" s="14" t="s">
+        <v>146</v>
+      </c>
+      <c r="H117" s="31" t="s">
+        <v>128</v>
+      </c>
+      <c r="I117" s="31"/>
+    </row>
+    <row r="118" spans="1:9" ht="33" customHeight="1">
+      <c r="A118" s="46" t="s">
+        <v>156</v>
+      </c>
+      <c r="B118" s="46"/>
+      <c r="C118" s="46"/>
+      <c r="D118" s="46"/>
+      <c r="G118" s="18" t="s">
+        <v>159</v>
+      </c>
+      <c r="H118" s="38" t="s">
+        <v>148</v>
+      </c>
+      <c r="I118" s="39"/>
+    </row>
+    <row r="119" spans="1:9" ht="26.25" customHeight="1">
+      <c r="A119" s="47" t="s">
+        <v>141</v>
+      </c>
+      <c r="B119" s="47"/>
+      <c r="C119" s="47"/>
+      <c r="D119" s="47"/>
+      <c r="G119" s="32" t="s">
         <v>157</v>
       </c>
-      <c r="H103" s="62" t="s">
+      <c r="H119" s="33"/>
+      <c r="I119" s="34"/>
+    </row>
+    <row r="120" spans="1:9" ht="32.25" customHeight="1">
+      <c r="G120" s="35" t="s">
+        <v>160</v>
+      </c>
+      <c r="H120" s="36"/>
+      <c r="I120" s="37"/>
+    </row>
+    <row r="121" spans="1:9" ht="26.25" customHeight="1">
+      <c r="G121" s="84" t="s">
+        <v>124</v>
+      </c>
+      <c r="H121" s="85"/>
+      <c r="I121" s="86"/>
+    </row>
+    <row r="122" spans="1:9" ht="24.75" customHeight="1">
+      <c r="G122" s="35" t="s">
+        <v>125</v>
+      </c>
+      <c r="H122" s="36"/>
+      <c r="I122" s="37"/>
+    </row>
+    <row r="123" spans="1:9" ht="26.25" customHeight="1">
+      <c r="G123" s="35" t="s">
         <v>158</v>
       </c>
-      <c r="I103" s="63"/>
-    </row>
-    <row r="104" spans="1:9" ht="39" customHeight="1">
-      <c r="A104" s="61" t="s">
-        <v>151</v>
-      </c>
-      <c r="B104" s="61"/>
-      <c r="C104" s="61"/>
-      <c r="D104" s="61"/>
-      <c r="G104" s="45" t="s">
+      <c r="H123" s="36"/>
+      <c r="I123" s="37"/>
+    </row>
+    <row r="124" spans="1:9" ht="28.5" customHeight="1"/>
+    <row r="126" spans="1:9" ht="43.5" customHeight="1" thickBot="1">
+      <c r="A126" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="H104" s="45"/>
-      <c r="I104" s="45"/>
-    </row>
-    <row r="105" spans="1:9" ht="30.75" customHeight="1">
-      <c r="G105" s="46" t="s">
+    </row>
+    <row r="127" spans="1:9" ht="36" customHeight="1" thickBot="1">
+      <c r="A127" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="B127" s="40" t="s">
+        <v>93</v>
+      </c>
+      <c r="C127" s="41"/>
+      <c r="D127" s="42"/>
+      <c r="G127" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="H127" s="52" t="s">
+        <v>102</v>
+      </c>
+      <c r="I127" s="53"/>
+    </row>
+    <row r="128" spans="1:9" ht="31.5" customHeight="1" thickBot="1">
+      <c r="A128" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="B128" s="17" t="s">
+        <v>144</v>
+      </c>
+      <c r="C128" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="D128" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="G128" s="21" t="s">
+        <v>103</v>
+      </c>
+      <c r="H128" s="87"/>
+      <c r="I128" s="88"/>
+    </row>
+    <row r="129" spans="1:9" ht="36" customHeight="1" thickBot="1">
+      <c r="A129" s="43" t="s">
+        <v>140</v>
+      </c>
+      <c r="B129" s="43"/>
+      <c r="C129" s="43"/>
+      <c r="D129" s="43"/>
+      <c r="G129" s="89" t="s">
+        <v>104</v>
+      </c>
+      <c r="H129" s="90"/>
+      <c r="I129" s="91"/>
+    </row>
+    <row r="130" spans="1:9" ht="30" customHeight="1" thickBot="1">
+      <c r="A130" s="31" t="s">
+        <v>139</v>
+      </c>
+      <c r="B130" s="31"/>
+      <c r="C130" s="31"/>
+      <c r="D130" s="31"/>
+      <c r="G130" s="54" t="s">
+        <v>105</v>
+      </c>
+      <c r="H130" s="55"/>
+      <c r="I130" s="56"/>
+    </row>
+    <row r="131" spans="1:9" ht="29.25" customHeight="1" thickBot="1">
+      <c r="A131" s="44" t="s">
+        <v>143</v>
+      </c>
+      <c r="B131" s="44"/>
+      <c r="C131" s="44"/>
+      <c r="D131" s="44"/>
+      <c r="G131" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="H131" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="I131" s="12" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="132" spans="1:9" ht="30.75" customHeight="1" thickBot="1">
+      <c r="A132" s="45" t="s">
+        <v>142</v>
+      </c>
+      <c r="B132" s="45"/>
+      <c r="C132" s="45"/>
+      <c r="D132" s="45"/>
+      <c r="G132" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="H132" s="63" t="s">
+        <v>128</v>
+      </c>
+      <c r="I132" s="65"/>
+    </row>
+    <row r="133" spans="1:9" ht="33.75" customHeight="1" thickBot="1">
+      <c r="A133" s="46" t="s">
         <v>163</v>
       </c>
-      <c r="H105" s="46"/>
-      <c r="I105" s="46"/>
-    </row>
-    <row r="108" spans="1:9" ht="35.25" customHeight="1">
-      <c r="A108" s="1" t="s">
+      <c r="B133" s="46"/>
+      <c r="C133" s="46"/>
+      <c r="D133" s="46"/>
+      <c r="G133" s="81" t="s">
+        <v>110</v>
+      </c>
+      <c r="H133" s="82"/>
+      <c r="I133" s="83"/>
+    </row>
+    <row r="134" spans="1:9" ht="34.5" customHeight="1" thickBot="1">
+      <c r="A134" s="47" t="s">
+        <v>141</v>
+      </c>
+      <c r="B134" s="47"/>
+      <c r="C134" s="47"/>
+      <c r="D134" s="47"/>
+      <c r="G134" s="78" t="s">
+        <v>164</v>
+      </c>
+      <c r="H134" s="79"/>
+      <c r="I134" s="80"/>
+    </row>
+    <row r="135" spans="1:9" ht="27" customHeight="1"/>
+    <row r="136" spans="1:9" ht="39" customHeight="1"/>
+    <row r="137" spans="1:9" ht="45.75" customHeight="1">
+      <c r="A137" s="1" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="109" spans="1:9" ht="31.5" customHeight="1">
-      <c r="A109" s="15" t="s">
-        <v>99</v>
-      </c>
-      <c r="B109" s="69" t="s">
-        <v>100</v>
-      </c>
-      <c r="C109" s="70"/>
-      <c r="D109" s="71"/>
-      <c r="G109" s="15" t="s">
+    <row r="138" spans="1:9" ht="36" customHeight="1">
+      <c r="A138" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="B138" s="40" t="s">
+        <v>93</v>
+      </c>
+      <c r="C138" s="41"/>
+      <c r="D138" s="42"/>
+      <c r="G138" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="H138" s="48" t="s">
+        <v>102</v>
+      </c>
+      <c r="I138" s="48"/>
+    </row>
+    <row r="139" spans="1:9" ht="32.25" customHeight="1">
+      <c r="A139" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="B139" s="17" t="s">
+        <v>144</v>
+      </c>
+      <c r="C139" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="D139" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="G139" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="H139" s="30"/>
+      <c r="I139" s="30"/>
+    </row>
+    <row r="140" spans="1:9" ht="36" customHeight="1">
+      <c r="A140" s="43" t="s">
+        <v>140</v>
+      </c>
+      <c r="B140" s="43"/>
+      <c r="C140" s="43"/>
+      <c r="D140" s="43"/>
+      <c r="G140" s="49" t="s">
+        <v>104</v>
+      </c>
+      <c r="H140" s="50"/>
+      <c r="I140" s="51"/>
+    </row>
+    <row r="141" spans="1:9" ht="31.5" customHeight="1">
+      <c r="A141" s="31" t="s">
+        <v>185</v>
+      </c>
+      <c r="B141" s="31"/>
+      <c r="C141" s="31"/>
+      <c r="D141" s="31"/>
+      <c r="G141" s="40" t="s">
+        <v>149</v>
+      </c>
+      <c r="H141" s="41"/>
+      <c r="I141" s="42"/>
+    </row>
+    <row r="142" spans="1:9" ht="29.25" customHeight="1">
+      <c r="A142" s="44" t="s">
+        <v>143</v>
+      </c>
+      <c r="B142" s="44"/>
+      <c r="C142" s="44"/>
+      <c r="D142" s="44"/>
+      <c r="G142" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="H142" s="16" t="s">
+        <v>107</v>
+      </c>
+      <c r="I142" s="16" t="s">
         <v>108</v>
       </c>
-      <c r="H109" s="64" t="s">
-        <v>109</v>
-      </c>
-      <c r="I109" s="64"/>
-    </row>
-    <row r="110" spans="1:9" ht="28.5">
-      <c r="A110" s="16" t="s">
+    </row>
+    <row r="143" spans="1:9" ht="27.75" customHeight="1">
+      <c r="A143" s="45" t="s">
+        <v>142</v>
+      </c>
+      <c r="B143" s="45"/>
+      <c r="C143" s="45"/>
+      <c r="D143" s="45"/>
+      <c r="G143" s="14" t="s">
+        <v>146</v>
+      </c>
+      <c r="H143" s="31" t="s">
+        <v>128</v>
+      </c>
+      <c r="I143" s="31"/>
+    </row>
+    <row r="144" spans="1:9" ht="31.5" customHeight="1">
+      <c r="A144" s="46" t="s">
+        <v>178</v>
+      </c>
+      <c r="B144" s="46"/>
+      <c r="C144" s="46"/>
+      <c r="D144" s="46"/>
+      <c r="G144" s="18" t="s">
+        <v>159</v>
+      </c>
+      <c r="H144" s="38" t="s">
+        <v>148</v>
+      </c>
+      <c r="I144" s="39"/>
+    </row>
+    <row r="145" spans="1:12" ht="29.25" customHeight="1">
+      <c r="A145" s="47" t="s">
+        <v>141</v>
+      </c>
+      <c r="B145" s="47"/>
+      <c r="C145" s="47"/>
+      <c r="D145" s="47"/>
+      <c r="G145" s="32" t="s">
+        <v>166</v>
+      </c>
+      <c r="H145" s="33"/>
+      <c r="I145" s="34"/>
+    </row>
+    <row r="146" spans="1:12" ht="34.5" customHeight="1">
+      <c r="G146" s="35" t="s">
+        <v>167</v>
+      </c>
+      <c r="H146" s="36"/>
+      <c r="I146" s="37"/>
+      <c r="K146" t="s">
+        <v>179</v>
+      </c>
+      <c r="L146" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="147" spans="1:12" ht="35.25" customHeight="1"/>
+    <row r="148" spans="1:12" ht="31.5" customHeight="1">
+      <c r="A148" s="1" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="149" spans="1:12" ht="39.75" customHeight="1">
+      <c r="A149" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="B149" s="40" t="s">
+        <v>93</v>
+      </c>
+      <c r="C149" s="41"/>
+      <c r="D149" s="42"/>
+      <c r="G149" s="15" t="s">
         <v>101</v>
       </c>
-      <c r="B110" s="17" t="s">
-        <v>154</v>
-      </c>
-      <c r="C110" s="16" t="s">
+      <c r="H149" s="48" t="s">
+        <v>102</v>
+      </c>
+      <c r="I149" s="48"/>
+    </row>
+    <row r="150" spans="1:12" ht="32.25" customHeight="1">
+      <c r="A150" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="B150" s="17" t="s">
+        <v>144</v>
+      </c>
+      <c r="C150" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="D150" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="G150" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="D110" s="16" t="s">
+      <c r="H150" s="30"/>
+      <c r="I150" s="30"/>
+    </row>
+    <row r="151" spans="1:12" ht="30" customHeight="1">
+      <c r="A151" s="43" t="s">
+        <v>140</v>
+      </c>
+      <c r="B151" s="43"/>
+      <c r="C151" s="43"/>
+      <c r="D151" s="43"/>
+      <c r="G151" s="49" t="s">
         <v>104</v>
       </c>
-      <c r="G110" s="16" t="s">
-        <v>110</v>
-      </c>
-      <c r="H110" s="65"/>
-      <c r="I110" s="65"/>
-    </row>
-    <row r="111" spans="1:9" ht="31.5" customHeight="1">
-      <c r="A111" s="44" t="s">
-        <v>150</v>
-      </c>
-      <c r="B111" s="44"/>
-      <c r="C111" s="44"/>
-      <c r="D111" s="44"/>
-      <c r="G111" s="66" t="s">
-        <v>111</v>
-      </c>
-      <c r="H111" s="66"/>
-      <c r="I111" s="66"/>
-    </row>
-    <row r="112" spans="1:9" ht="30" customHeight="1">
-      <c r="A112" s="45" t="s">
+      <c r="H151" s="50"/>
+      <c r="I151" s="51"/>
+    </row>
+    <row r="152" spans="1:12" ht="28.5" customHeight="1">
+      <c r="A152" s="31" t="s">
+        <v>205</v>
+      </c>
+      <c r="B152" s="31"/>
+      <c r="C152" s="31"/>
+      <c r="D152" s="31"/>
+      <c r="G152" s="40" t="s">
         <v>149</v>
       </c>
-      <c r="B112" s="45"/>
-      <c r="C112" s="45"/>
-      <c r="D112" s="45"/>
-      <c r="G112" s="67" t="s">
-        <v>112</v>
-      </c>
-      <c r="H112" s="67"/>
-      <c r="I112" s="67"/>
-    </row>
-    <row r="113" spans="1:9" ht="26.25" customHeight="1">
-      <c r="A113" s="59" t="s">
-        <v>153</v>
-      </c>
-      <c r="B113" s="59"/>
-      <c r="C113" s="59"/>
-      <c r="D113" s="59"/>
-      <c r="G113" s="16" t="s">
-        <v>113</v>
-      </c>
-      <c r="H113" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="I113" s="16" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="114" spans="1:9" ht="27" customHeight="1">
-      <c r="A114" s="60" t="s">
-        <v>152</v>
-      </c>
-      <c r="B114" s="60"/>
-      <c r="C114" s="60"/>
-      <c r="D114" s="60"/>
-      <c r="G114" s="45" t="s">
-        <v>167</v>
-      </c>
-      <c r="H114" s="45"/>
-      <c r="I114" s="45"/>
-    </row>
-    <row r="115" spans="1:9" ht="27.75" customHeight="1">
-      <c r="A115" s="46" t="s">
-        <v>166</v>
-      </c>
-      <c r="B115" s="46"/>
-      <c r="C115" s="46"/>
-      <c r="D115" s="46"/>
-    </row>
-    <row r="116" spans="1:9" ht="26.25" customHeight="1">
-      <c r="A116" s="61" t="s">
-        <v>151</v>
-      </c>
-      <c r="B116" s="61"/>
-      <c r="C116" s="61"/>
-      <c r="D116" s="61"/>
-    </row>
-    <row r="120" spans="1:9" ht="52.5" customHeight="1">
-      <c r="A120" s="1" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="121" spans="1:9" ht="37.5" customHeight="1">
-      <c r="A121" s="15" t="s">
-        <v>99</v>
-      </c>
-      <c r="B121" s="69" t="s">
-        <v>100</v>
-      </c>
-      <c r="C121" s="70"/>
-      <c r="D121" s="71"/>
-      <c r="G121" s="15" t="s">
+      <c r="H152" s="41"/>
+      <c r="I152" s="42"/>
+    </row>
+    <row r="153" spans="1:12" ht="24" customHeight="1">
+      <c r="A153" s="44" t="s">
+        <v>143</v>
+      </c>
+      <c r="B153" s="44"/>
+      <c r="C153" s="44"/>
+      <c r="D153" s="44"/>
+      <c r="G153" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="H153" s="16" t="s">
+        <v>107</v>
+      </c>
+      <c r="I153" s="16" t="s">
         <v>108</v>
       </c>
-      <c r="H121" s="64" t="s">
-        <v>109</v>
-      </c>
-      <c r="I121" s="64"/>
-    </row>
-    <row r="122" spans="1:9" ht="35.25" customHeight="1">
-      <c r="A122" s="16" t="s">
+    </row>
+    <row r="154" spans="1:12" ht="29.25" customHeight="1">
+      <c r="A154" s="45" t="s">
+        <v>142</v>
+      </c>
+      <c r="B154" s="45"/>
+      <c r="C154" s="45"/>
+      <c r="D154" s="45"/>
+      <c r="G154" s="14" t="s">
+        <v>146</v>
+      </c>
+      <c r="H154" s="31" t="s">
+        <v>128</v>
+      </c>
+      <c r="I154" s="31"/>
+    </row>
+    <row r="155" spans="1:12" ht="31.5" customHeight="1">
+      <c r="A155" s="46" t="s">
+        <v>206</v>
+      </c>
+      <c r="B155" s="46"/>
+      <c r="C155" s="46"/>
+      <c r="D155" s="46"/>
+      <c r="G155" s="18" t="s">
+        <v>159</v>
+      </c>
+      <c r="H155" s="38" t="s">
+        <v>148</v>
+      </c>
+      <c r="I155" s="39"/>
+    </row>
+    <row r="156" spans="1:12" ht="28.5" customHeight="1">
+      <c r="A156" s="47" t="s">
+        <v>141</v>
+      </c>
+      <c r="B156" s="47"/>
+      <c r="C156" s="47"/>
+      <c r="D156" s="47"/>
+      <c r="G156" s="32" t="s">
+        <v>169</v>
+      </c>
+      <c r="H156" s="33"/>
+      <c r="I156" s="34"/>
+    </row>
+    <row r="157" spans="1:12" ht="30" customHeight="1">
+      <c r="G157" s="35" t="s">
+        <v>170</v>
+      </c>
+      <c r="H157" s="36"/>
+      <c r="I157" s="37"/>
+    </row>
+    <row r="160" spans="1:12">
+      <c r="A160" s="1" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="161" spans="1:9" ht="33.75" customHeight="1">
+      <c r="A161" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="B161" s="40" t="s">
+        <v>93</v>
+      </c>
+      <c r="C161" s="41"/>
+      <c r="D161" s="42"/>
+      <c r="G161" s="15" t="s">
         <v>101</v>
       </c>
-      <c r="B122" s="17" t="s">
-        <v>154</v>
-      </c>
-      <c r="C122" s="16" t="s">
+      <c r="H161" s="48" t="s">
+        <v>102</v>
+      </c>
+      <c r="I161" s="48"/>
+    </row>
+    <row r="162" spans="1:9" ht="28.5">
+      <c r="A162" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="B162" s="17" t="s">
+        <v>144</v>
+      </c>
+      <c r="C162" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="D162" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="G162" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="D122" s="16" t="s">
+      <c r="H162" s="30"/>
+      <c r="I162" s="30"/>
+    </row>
+    <row r="163" spans="1:9" ht="29.25" customHeight="1">
+      <c r="A163" s="43" t="s">
+        <v>140</v>
+      </c>
+      <c r="B163" s="43"/>
+      <c r="C163" s="43"/>
+      <c r="D163" s="43"/>
+      <c r="G163" s="49" t="s">
         <v>104</v>
       </c>
-      <c r="G122" s="16" t="s">
-        <v>110</v>
-      </c>
-      <c r="H122" s="65"/>
-      <c r="I122" s="65"/>
-    </row>
-    <row r="123" spans="1:9" ht="31.5" customHeight="1">
-      <c r="A123" s="44" t="s">
-        <v>150</v>
-      </c>
-      <c r="B123" s="44"/>
-      <c r="C123" s="44"/>
-      <c r="D123" s="44"/>
-      <c r="G123" s="66" t="s">
-        <v>111</v>
-      </c>
-      <c r="H123" s="66"/>
-      <c r="I123" s="66"/>
-    </row>
-    <row r="124" spans="1:9" ht="32.25" customHeight="1">
-      <c r="A124" s="45" t="s">
+      <c r="H163" s="50"/>
+      <c r="I163" s="51"/>
+    </row>
+    <row r="164" spans="1:9" ht="27" customHeight="1">
+      <c r="A164" s="31" t="s">
+        <v>172</v>
+      </c>
+      <c r="B164" s="31"/>
+      <c r="C164" s="31"/>
+      <c r="D164" s="31"/>
+      <c r="G164" s="40" t="s">
         <v>149</v>
       </c>
-      <c r="B124" s="45"/>
-      <c r="C124" s="45"/>
-      <c r="D124" s="45"/>
-      <c r="G124" s="67" t="s">
+      <c r="H164" s="41"/>
+      <c r="I164" s="42"/>
+    </row>
+    <row r="165" spans="1:9" ht="26.25" customHeight="1">
+      <c r="A165" s="44" t="s">
+        <v>143</v>
+      </c>
+      <c r="B165" s="44"/>
+      <c r="C165" s="44"/>
+      <c r="D165" s="44"/>
+      <c r="G165" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="H165" s="16" t="s">
+        <v>107</v>
+      </c>
+      <c r="I165" s="16" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="166" spans="1:9" ht="29.25" customHeight="1">
+      <c r="A166" s="45" t="s">
+        <v>142</v>
+      </c>
+      <c r="B166" s="45"/>
+      <c r="C166" s="45"/>
+      <c r="D166" s="45"/>
+      <c r="G166" s="14" t="s">
+        <v>146</v>
+      </c>
+      <c r="H166" s="31" t="s">
+        <v>128</v>
+      </c>
+      <c r="I166" s="31"/>
+    </row>
+    <row r="167" spans="1:9" ht="24.75" customHeight="1">
+      <c r="A167" s="46" t="s">
+        <v>173</v>
+      </c>
+      <c r="B167" s="46"/>
+      <c r="C167" s="46"/>
+      <c r="D167" s="46"/>
+      <c r="G167" s="18" t="s">
         <v>159</v>
       </c>
-      <c r="H124" s="67"/>
-      <c r="I124" s="67"/>
-    </row>
-    <row r="125" spans="1:9" ht="29.25" customHeight="1">
-      <c r="A125" s="59" t="s">
-        <v>153</v>
-      </c>
-      <c r="B125" s="59"/>
-      <c r="C125" s="59"/>
-      <c r="D125" s="59"/>
-      <c r="G125" s="16" t="s">
-        <v>113</v>
-      </c>
-      <c r="H125" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="I125" s="16" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="126" spans="1:9" ht="27.75" customHeight="1">
-      <c r="A126" s="60" t="s">
-        <v>152</v>
-      </c>
-      <c r="B126" s="60"/>
-      <c r="C126" s="60"/>
-      <c r="D126" s="60"/>
-      <c r="G126" s="14" t="s">
-        <v>156</v>
-      </c>
-      <c r="H126" s="45" t="s">
-        <v>135</v>
-      </c>
-      <c r="I126" s="45"/>
-    </row>
-    <row r="127" spans="1:9" ht="33" customHeight="1">
-      <c r="A127" s="46" t="s">
-        <v>169</v>
-      </c>
-      <c r="B127" s="46"/>
-      <c r="C127" s="46"/>
-      <c r="D127" s="46"/>
-      <c r="G127" s="18" t="s">
-        <v>172</v>
-      </c>
-      <c r="H127" s="62" t="s">
-        <v>158</v>
-      </c>
-      <c r="I127" s="63"/>
-    </row>
-    <row r="128" spans="1:9" ht="26.25" customHeight="1">
-      <c r="A128" s="61" t="s">
-        <v>151</v>
-      </c>
-      <c r="B128" s="61"/>
-      <c r="C128" s="61"/>
-      <c r="D128" s="61"/>
-      <c r="G128" s="41" t="s">
-        <v>170</v>
-      </c>
-      <c r="H128" s="42"/>
-      <c r="I128" s="43"/>
-    </row>
-    <row r="129" spans="1:9" ht="32.25" customHeight="1">
-      <c r="G129" s="46" t="s">
-        <v>173</v>
-      </c>
-      <c r="H129" s="46"/>
-      <c r="I129" s="46"/>
-    </row>
-    <row r="130" spans="1:9" ht="26.25" customHeight="1">
-      <c r="G130" s="68" t="s">
-        <v>131</v>
-      </c>
-      <c r="H130" s="68"/>
-      <c r="I130" s="68"/>
-    </row>
-    <row r="131" spans="1:9" ht="24.75" customHeight="1">
-      <c r="G131" s="46" t="s">
-        <v>132</v>
-      </c>
-      <c r="H131" s="46"/>
-      <c r="I131" s="46"/>
-    </row>
-    <row r="132" spans="1:9" ht="26.25" customHeight="1">
-      <c r="G132" s="46" t="s">
-        <v>171</v>
-      </c>
-      <c r="H132" s="46"/>
-      <c r="I132" s="46"/>
-    </row>
-    <row r="133" spans="1:9" ht="28.5" customHeight="1"/>
-    <row r="135" spans="1:9" ht="43.5" customHeight="1" thickBot="1">
-      <c r="A135" s="1" t="s">
+      <c r="H167" s="38" t="s">
+        <v>148</v>
+      </c>
+      <c r="I167" s="39"/>
+    </row>
+    <row r="168" spans="1:9" ht="28.5" customHeight="1">
+      <c r="A168" s="47" t="s">
+        <v>141</v>
+      </c>
+      <c r="B168" s="47"/>
+      <c r="C168" s="47"/>
+      <c r="D168" s="47"/>
+      <c r="G168" s="32" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="136" spans="1:9" ht="36" customHeight="1" thickBot="1">
-      <c r="A136" s="15" t="s">
-        <v>99</v>
-      </c>
-      <c r="B136" s="69" t="s">
-        <v>100</v>
-      </c>
-      <c r="C136" s="70"/>
-      <c r="D136" s="71"/>
-      <c r="G136" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="H136" s="72" t="s">
-        <v>109</v>
-      </c>
-      <c r="I136" s="73"/>
-    </row>
-    <row r="137" spans="1:9" ht="31.5" customHeight="1" thickBot="1">
-      <c r="A137" s="16" t="s">
-        <v>101</v>
-      </c>
-      <c r="B137" s="17" t="s">
-        <v>154</v>
-      </c>
-      <c r="C137" s="16" t="s">
-        <v>103</v>
-      </c>
-      <c r="D137" s="16" t="s">
-        <v>104</v>
-      </c>
-      <c r="G137" s="21" t="s">
-        <v>110</v>
-      </c>
-      <c r="H137" s="74"/>
-      <c r="I137" s="75"/>
-    </row>
-    <row r="138" spans="1:9" ht="36" customHeight="1" thickBot="1">
-      <c r="A138" s="44" t="s">
-        <v>150</v>
-      </c>
-      <c r="B138" s="44"/>
-      <c r="C138" s="44"/>
-      <c r="D138" s="44"/>
-      <c r="G138" s="51" t="s">
-        <v>111</v>
-      </c>
-      <c r="H138" s="76"/>
-      <c r="I138" s="77"/>
-    </row>
-    <row r="139" spans="1:9" ht="30" customHeight="1" thickBot="1">
-      <c r="A139" s="45" t="s">
-        <v>149</v>
-      </c>
-      <c r="B139" s="45"/>
-      <c r="C139" s="45"/>
-      <c r="D139" s="45"/>
-      <c r="G139" s="35" t="s">
-        <v>112</v>
-      </c>
-      <c r="H139" s="36"/>
-      <c r="I139" s="37"/>
-    </row>
-    <row r="140" spans="1:9" ht="29.25" customHeight="1" thickBot="1">
-      <c r="A140" s="59" t="s">
-        <v>153</v>
-      </c>
-      <c r="B140" s="59"/>
-      <c r="C140" s="59"/>
-      <c r="D140" s="59"/>
-      <c r="G140" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="H140" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="I140" s="12" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="141" spans="1:9" ht="30.75" customHeight="1" thickBot="1">
-      <c r="A141" s="60" t="s">
-        <v>152</v>
-      </c>
-      <c r="B141" s="60"/>
-      <c r="C141" s="60"/>
-      <c r="D141" s="60"/>
-      <c r="G141" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="H141" s="29" t="s">
-        <v>135</v>
-      </c>
-      <c r="I141" s="30"/>
-    </row>
-    <row r="142" spans="1:9" ht="33.75" customHeight="1" thickBot="1">
-      <c r="A142" s="46" t="s">
+      <c r="H168" s="33"/>
+      <c r="I168" s="34"/>
+    </row>
+    <row r="169" spans="1:9" ht="28.5" customHeight="1">
+      <c r="G169" s="32" t="s">
+        <v>177</v>
+      </c>
+      <c r="H169" s="33"/>
+      <c r="I169" s="34"/>
+    </row>
+    <row r="170" spans="1:9" ht="28.5" customHeight="1">
+      <c r="G170" s="32" t="s">
         <v>176</v>
       </c>
-      <c r="B142" s="46"/>
-      <c r="C142" s="46"/>
-      <c r="D142" s="46"/>
-      <c r="G142" s="81" t="s">
-        <v>117</v>
-      </c>
-      <c r="H142" s="82"/>
-      <c r="I142" s="83"/>
-    </row>
-    <row r="143" spans="1:9" ht="34.5" customHeight="1" thickBot="1">
-      <c r="A143" s="61" t="s">
-        <v>151</v>
-      </c>
-      <c r="B143" s="61"/>
-      <c r="C143" s="61"/>
-      <c r="D143" s="61"/>
-      <c r="G143" s="78" t="s">
-        <v>177</v>
-      </c>
-      <c r="H143" s="79"/>
-      <c r="I143" s="80"/>
-    </row>
-    <row r="144" spans="1:9" ht="27" customHeight="1"/>
-    <row r="145" spans="1:9" ht="39" customHeight="1"/>
-    <row r="146" spans="1:9" ht="45.75" customHeight="1">
-      <c r="A146" s="1" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="147" spans="1:9" ht="40.5" customHeight="1">
-      <c r="A147" s="15" t="s">
-        <v>99</v>
-      </c>
-      <c r="B147" s="69" t="s">
-        <v>100</v>
-      </c>
-      <c r="C147" s="70"/>
-      <c r="D147" s="71"/>
-    </row>
-    <row r="148" spans="1:9" ht="28.5">
-      <c r="A148" s="16" t="s">
-        <v>101</v>
-      </c>
-      <c r="B148" s="17" t="s">
-        <v>154</v>
-      </c>
-      <c r="C148" s="16" t="s">
-        <v>103</v>
-      </c>
-      <c r="D148" s="16" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="149" spans="1:9" ht="34.5" customHeight="1">
-      <c r="A149" s="44" t="s">
-        <v>150</v>
-      </c>
-      <c r="B149" s="44"/>
-      <c r="C149" s="44"/>
-      <c r="D149" s="44"/>
-      <c r="G149" s="1" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="150" spans="1:9" ht="29.25" customHeight="1">
-      <c r="A150" s="45" t="s">
-        <v>149</v>
-      </c>
-      <c r="B150" s="45"/>
-      <c r="C150" s="45"/>
-      <c r="D150" s="45"/>
-    </row>
-    <row r="151" spans="1:9" ht="32.25" customHeight="1">
-      <c r="A151" s="59" t="s">
-        <v>153</v>
-      </c>
-      <c r="B151" s="59"/>
-      <c r="C151" s="59"/>
-      <c r="D151" s="59"/>
-    </row>
-    <row r="152" spans="1:9" ht="32.25" customHeight="1">
-      <c r="A152" s="60" t="s">
-        <v>152</v>
-      </c>
-      <c r="B152" s="60"/>
-      <c r="C152" s="60"/>
-      <c r="D152" s="60"/>
-    </row>
-    <row r="153" spans="1:9" ht="30" customHeight="1">
-      <c r="A153" s="46" t="s">
-        <v>178</v>
-      </c>
-      <c r="B153" s="46"/>
-      <c r="C153" s="46"/>
-      <c r="D153" s="46"/>
-    </row>
-    <row r="154" spans="1:9" ht="30.75" customHeight="1">
-      <c r="A154" s="61" t="s">
-        <v>151</v>
-      </c>
-      <c r="B154" s="61"/>
-      <c r="C154" s="61"/>
-      <c r="D154" s="61"/>
-    </row>
-    <row r="157" spans="1:9" ht="45.75" customHeight="1">
-      <c r="A157" s="1" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="158" spans="1:9" ht="36" customHeight="1">
-      <c r="A158" s="15" t="s">
-        <v>99</v>
-      </c>
-      <c r="B158" s="69" t="s">
-        <v>100</v>
-      </c>
-      <c r="C158" s="70"/>
-      <c r="D158" s="71"/>
-      <c r="G158" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="H158" s="64" t="s">
-        <v>109</v>
-      </c>
-      <c r="I158" s="64"/>
-    </row>
-    <row r="159" spans="1:9" ht="32.25" customHeight="1">
-      <c r="A159" s="16" t="s">
-        <v>101</v>
-      </c>
-      <c r="B159" s="17" t="s">
-        <v>154</v>
-      </c>
-      <c r="C159" s="16" t="s">
-        <v>103</v>
-      </c>
-      <c r="D159" s="16" t="s">
-        <v>104</v>
-      </c>
-      <c r="G159" s="16" t="s">
-        <v>110</v>
-      </c>
-      <c r="H159" s="65"/>
-      <c r="I159" s="65"/>
-    </row>
-    <row r="160" spans="1:9" ht="36" customHeight="1">
-      <c r="A160" s="44" t="s">
-        <v>150</v>
-      </c>
-      <c r="B160" s="44"/>
-      <c r="C160" s="44"/>
-      <c r="D160" s="44"/>
-      <c r="G160" s="66" t="s">
-        <v>111</v>
-      </c>
-      <c r="H160" s="66"/>
-      <c r="I160" s="66"/>
-    </row>
-    <row r="161" spans="1:12" ht="31.5" customHeight="1">
-      <c r="A161" s="45" t="s">
-        <v>202</v>
-      </c>
-      <c r="B161" s="45"/>
-      <c r="C161" s="45"/>
-      <c r="D161" s="45"/>
-      <c r="G161" s="67" t="s">
-        <v>159</v>
-      </c>
-      <c r="H161" s="67"/>
-      <c r="I161" s="67"/>
-    </row>
-    <row r="162" spans="1:12" ht="29.25" customHeight="1">
-      <c r="A162" s="59" t="s">
-        <v>153</v>
-      </c>
-      <c r="B162" s="59"/>
-      <c r="C162" s="59"/>
-      <c r="D162" s="59"/>
-      <c r="G162" s="16" t="s">
-        <v>113</v>
-      </c>
-      <c r="H162" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="I162" s="16" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="163" spans="1:12" ht="27.75" customHeight="1">
-      <c r="A163" s="60" t="s">
-        <v>152</v>
-      </c>
-      <c r="B163" s="60"/>
-      <c r="C163" s="60"/>
-      <c r="D163" s="60"/>
-      <c r="G163" s="14" t="s">
-        <v>156</v>
-      </c>
-      <c r="H163" s="45" t="s">
-        <v>135</v>
-      </c>
-      <c r="I163" s="45"/>
-    </row>
-    <row r="164" spans="1:12" ht="31.5" customHeight="1">
-      <c r="A164" s="46" t="s">
-        <v>194</v>
-      </c>
-      <c r="B164" s="46"/>
-      <c r="C164" s="46"/>
-      <c r="D164" s="46"/>
-      <c r="G164" s="18" t="s">
-        <v>172</v>
-      </c>
-      <c r="H164" s="62" t="s">
-        <v>158</v>
-      </c>
-      <c r="I164" s="63"/>
-    </row>
-    <row r="165" spans="1:12" ht="29.25" customHeight="1">
-      <c r="A165" s="61" t="s">
-        <v>151</v>
-      </c>
-      <c r="B165" s="61"/>
-      <c r="C165" s="61"/>
-      <c r="D165" s="61"/>
-      <c r="G165" s="41" t="s">
-        <v>181</v>
-      </c>
-      <c r="H165" s="42"/>
-      <c r="I165" s="43"/>
-    </row>
-    <row r="166" spans="1:12" ht="34.5" customHeight="1">
-      <c r="G166" s="46" t="s">
-        <v>182</v>
-      </c>
-      <c r="H166" s="46"/>
-      <c r="I166" s="46"/>
-      <c r="K166" t="s">
-        <v>195</v>
-      </c>
-      <c r="L166" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="167" spans="1:12" ht="35.25" customHeight="1"/>
-    <row r="168" spans="1:12" ht="31.5" customHeight="1">
-      <c r="A168" s="1" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="169" spans="1:12" ht="39.75" customHeight="1">
-      <c r="A169" s="15" t="s">
-        <v>99</v>
-      </c>
-      <c r="B169" s="69" t="s">
-        <v>100</v>
-      </c>
-      <c r="C169" s="70"/>
-      <c r="D169" s="71"/>
-      <c r="G169" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="H169" s="64" t="s">
-        <v>109</v>
-      </c>
-      <c r="I169" s="64"/>
-    </row>
-    <row r="170" spans="1:12" ht="32.25" customHeight="1">
-      <c r="A170" s="16" t="s">
-        <v>101</v>
-      </c>
-      <c r="B170" s="17" t="s">
-        <v>154</v>
-      </c>
-      <c r="C170" s="16" t="s">
-        <v>103</v>
-      </c>
-      <c r="D170" s="16" t="s">
-        <v>104</v>
-      </c>
-      <c r="G170" s="16" t="s">
-        <v>110</v>
-      </c>
-      <c r="H170" s="65"/>
-      <c r="I170" s="65"/>
-    </row>
-    <row r="171" spans="1:12" ht="30" customHeight="1">
-      <c r="A171" s="44" t="s">
-        <v>150</v>
-      </c>
-      <c r="B171" s="44"/>
-      <c r="C171" s="44"/>
-      <c r="D171" s="44"/>
-      <c r="G171" s="66" t="s">
-        <v>111</v>
-      </c>
-      <c r="H171" s="66"/>
-      <c r="I171" s="66"/>
-    </row>
-    <row r="172" spans="1:12" ht="28.5" customHeight="1">
-      <c r="A172" s="45" t="s">
-        <v>188</v>
-      </c>
-      <c r="B172" s="45"/>
-      <c r="C172" s="45"/>
-      <c r="D172" s="45"/>
-      <c r="G172" s="67" t="s">
-        <v>159</v>
-      </c>
-      <c r="H172" s="67"/>
-      <c r="I172" s="67"/>
-    </row>
-    <row r="173" spans="1:12" ht="24" customHeight="1">
-      <c r="A173" s="59" t="s">
-        <v>153</v>
-      </c>
-      <c r="B173" s="59"/>
-      <c r="C173" s="59"/>
-      <c r="D173" s="59"/>
-      <c r="G173" s="16" t="s">
-        <v>113</v>
-      </c>
-      <c r="H173" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="I173" s="16" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="174" spans="1:12" ht="29.25" customHeight="1">
-      <c r="A174" s="60" t="s">
-        <v>152</v>
-      </c>
-      <c r="B174" s="60"/>
-      <c r="C174" s="60"/>
-      <c r="D174" s="60"/>
-      <c r="G174" s="14" t="s">
-        <v>156</v>
-      </c>
-      <c r="H174" s="45" t="s">
-        <v>135</v>
-      </c>
-      <c r="I174" s="45"/>
-    </row>
-    <row r="175" spans="1:12" ht="31.5" customHeight="1">
-      <c r="A175" s="46" t="s">
-        <v>186</v>
-      </c>
-      <c r="B175" s="46"/>
-      <c r="C175" s="46"/>
-      <c r="D175" s="46"/>
-      <c r="G175" s="18" t="s">
-        <v>172</v>
-      </c>
-      <c r="H175" s="62" t="s">
-        <v>158</v>
-      </c>
-      <c r="I175" s="63"/>
-    </row>
-    <row r="176" spans="1:12" ht="28.5" customHeight="1">
-      <c r="A176" s="61" t="s">
-        <v>151</v>
-      </c>
-      <c r="B176" s="61"/>
-      <c r="C176" s="61"/>
-      <c r="D176" s="61"/>
-      <c r="G176" s="41" t="s">
-        <v>184</v>
-      </c>
-      <c r="H176" s="42"/>
-      <c r="I176" s="43"/>
-    </row>
-    <row r="177" spans="1:9" ht="30" customHeight="1">
-      <c r="G177" s="46" t="s">
-        <v>185</v>
-      </c>
-      <c r="H177" s="46"/>
-      <c r="I177" s="46"/>
-    </row>
-    <row r="180" spans="1:9">
-      <c r="A180" s="1" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="181" spans="1:9" ht="33.75" customHeight="1">
-      <c r="A181" s="15" t="s">
-        <v>99</v>
-      </c>
-      <c r="B181" s="69" t="s">
-        <v>100</v>
-      </c>
-      <c r="C181" s="70"/>
-      <c r="D181" s="71"/>
-      <c r="G181" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="H181" s="64" t="s">
-        <v>109</v>
-      </c>
-      <c r="I181" s="64"/>
-    </row>
-    <row r="182" spans="1:9" ht="28.5">
-      <c r="A182" s="16" t="s">
-        <v>101</v>
-      </c>
-      <c r="B182" s="17" t="s">
-        <v>154</v>
-      </c>
-      <c r="C182" s="16" t="s">
-        <v>103</v>
-      </c>
-      <c r="D182" s="16" t="s">
-        <v>104</v>
-      </c>
-      <c r="G182" s="16" t="s">
-        <v>110</v>
-      </c>
-      <c r="H182" s="65"/>
-      <c r="I182" s="65"/>
-    </row>
-    <row r="183" spans="1:9" ht="29.25" customHeight="1">
-      <c r="A183" s="44" t="s">
-        <v>150</v>
-      </c>
-      <c r="B183" s="44"/>
-      <c r="C183" s="44"/>
-      <c r="D183" s="44"/>
-      <c r="G183" s="66" t="s">
-        <v>111</v>
-      </c>
-      <c r="H183" s="66"/>
-      <c r="I183" s="66"/>
-    </row>
-    <row r="184" spans="1:9" ht="27" customHeight="1">
-      <c r="A184" s="45" t="s">
-        <v>188</v>
-      </c>
-      <c r="B184" s="45"/>
-      <c r="C184" s="45"/>
-      <c r="D184" s="45"/>
-      <c r="G184" s="67" t="s">
-        <v>159</v>
-      </c>
-      <c r="H184" s="67"/>
-      <c r="I184" s="67"/>
-    </row>
-    <row r="185" spans="1:9" ht="26.25" customHeight="1">
-      <c r="A185" s="59" t="s">
-        <v>153</v>
-      </c>
-      <c r="B185" s="59"/>
-      <c r="C185" s="59"/>
-      <c r="D185" s="59"/>
-      <c r="G185" s="16" t="s">
-        <v>113</v>
-      </c>
-      <c r="H185" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="I185" s="16" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="186" spans="1:9" ht="29.25" customHeight="1">
-      <c r="A186" s="60" t="s">
-        <v>152</v>
-      </c>
-      <c r="B186" s="60"/>
-      <c r="C186" s="60"/>
-      <c r="D186" s="60"/>
-      <c r="G186" s="14" t="s">
-        <v>156</v>
-      </c>
-      <c r="H186" s="45" t="s">
-        <v>135</v>
-      </c>
-      <c r="I186" s="45"/>
-    </row>
-    <row r="187" spans="1:9" ht="24.75" customHeight="1">
-      <c r="A187" s="46" t="s">
-        <v>189</v>
-      </c>
-      <c r="B187" s="46"/>
-      <c r="C187" s="46"/>
-      <c r="D187" s="46"/>
-      <c r="G187" s="18" t="s">
-        <v>172</v>
-      </c>
-      <c r="H187" s="62" t="s">
-        <v>158</v>
-      </c>
-      <c r="I187" s="63"/>
-    </row>
-    <row r="188" spans="1:9" ht="28.5" customHeight="1">
-      <c r="A188" s="61" t="s">
-        <v>151</v>
-      </c>
-      <c r="B188" s="61"/>
-      <c r="C188" s="61"/>
-      <c r="D188" s="61"/>
-      <c r="G188" s="41" t="s">
-        <v>191</v>
-      </c>
-      <c r="H188" s="42"/>
-      <c r="I188" s="43"/>
-    </row>
-    <row r="189" spans="1:9" ht="28.5" customHeight="1">
-      <c r="G189" s="41" t="s">
-        <v>193</v>
-      </c>
-      <c r="H189" s="42"/>
-      <c r="I189" s="43"/>
-    </row>
-    <row r="190" spans="1:9" ht="28.5" customHeight="1">
-      <c r="G190" s="41" t="s">
-        <v>192</v>
-      </c>
-      <c r="H190" s="42"/>
-      <c r="I190" s="43"/>
-    </row>
-    <row r="191" spans="1:9" ht="28.5" customHeight="1">
-      <c r="G191" s="41" t="s">
-        <v>192</v>
-      </c>
-      <c r="H191" s="42"/>
-      <c r="I191" s="43"/>
-    </row>
-    <row r="192" spans="1:9" ht="27.75" customHeight="1">
-      <c r="G192" s="46" t="s">
-        <v>190</v>
-      </c>
-      <c r="H192" s="46"/>
-      <c r="I192" s="46"/>
-    </row>
-    <row r="195" ht="48" customHeight="1"/>
-    <row r="196" ht="29.25" customHeight="1"/>
-    <row r="197" ht="33" customHeight="1"/>
-    <row r="198" ht="33" customHeight="1"/>
-    <row r="199" ht="29.25" customHeight="1"/>
-    <row r="200" ht="29.25" customHeight="1"/>
-    <row r="201" ht="27.75" customHeight="1"/>
-    <row r="202" ht="30.75" customHeight="1"/>
-    <row r="203" ht="25.5" customHeight="1"/>
+      <c r="H170" s="33"/>
+      <c r="I170" s="34"/>
+    </row>
+    <row r="171" spans="1:9" ht="28.5" customHeight="1">
+      <c r="G171" s="32" t="s">
+        <v>176</v>
+      </c>
+      <c r="H171" s="33"/>
+      <c r="I171" s="34"/>
+    </row>
+    <row r="172" spans="1:9" ht="27.75" customHeight="1">
+      <c r="G172" s="35" t="s">
+        <v>174</v>
+      </c>
+      <c r="H172" s="36"/>
+      <c r="I172" s="37"/>
+    </row>
+    <row r="175" spans="1:9" ht="48" customHeight="1"/>
+    <row r="176" spans="1:9" ht="29.25" customHeight="1"/>
+    <row r="177" ht="33" customHeight="1"/>
+    <row r="178" ht="33" customHeight="1"/>
+    <row r="179" ht="29.25" customHeight="1"/>
+    <row r="180" ht="29.25" customHeight="1"/>
+    <row r="181" ht="27.75" customHeight="1"/>
+    <row r="182" ht="30.75" customHeight="1"/>
+    <row r="183" ht="25.5" customHeight="1"/>
   </sheetData>
-  <mergeCells count="218">
-    <mergeCell ref="H78:I78"/>
+  <mergeCells count="199">
+    <mergeCell ref="G80:I80"/>
     <mergeCell ref="G79:I79"/>
-    <mergeCell ref="G80:I80"/>
-    <mergeCell ref="A76:D76"/>
-    <mergeCell ref="H72:I72"/>
-    <mergeCell ref="H73:I73"/>
+    <mergeCell ref="G75:I75"/>
     <mergeCell ref="G74:I74"/>
-    <mergeCell ref="G75:I75"/>
-    <mergeCell ref="H77:I77"/>
-    <mergeCell ref="H187:I187"/>
-    <mergeCell ref="G188:I188"/>
-    <mergeCell ref="G192:I192"/>
-    <mergeCell ref="G190:I190"/>
-    <mergeCell ref="G191:I191"/>
-    <mergeCell ref="G189:I189"/>
-    <mergeCell ref="B181:D181"/>
-    <mergeCell ref="A183:D183"/>
-    <mergeCell ref="A184:D184"/>
-    <mergeCell ref="A185:D185"/>
-    <mergeCell ref="A186:D186"/>
-    <mergeCell ref="A187:D187"/>
-    <mergeCell ref="A188:D188"/>
-    <mergeCell ref="H181:I181"/>
-    <mergeCell ref="H175:I175"/>
-    <mergeCell ref="G176:I176"/>
-    <mergeCell ref="G177:I177"/>
-    <mergeCell ref="H182:I182"/>
-    <mergeCell ref="G183:I183"/>
-    <mergeCell ref="G184:I184"/>
-    <mergeCell ref="H186:I186"/>
-    <mergeCell ref="A172:D172"/>
-    <mergeCell ref="A173:D173"/>
-    <mergeCell ref="A174:D174"/>
-    <mergeCell ref="A175:D175"/>
-    <mergeCell ref="A176:D176"/>
-    <mergeCell ref="H169:I169"/>
-    <mergeCell ref="H170:I170"/>
-    <mergeCell ref="G171:I171"/>
-    <mergeCell ref="G172:I172"/>
-    <mergeCell ref="H174:I174"/>
-    <mergeCell ref="G166:I166"/>
-    <mergeCell ref="B169:D169"/>
-    <mergeCell ref="A171:D171"/>
-    <mergeCell ref="A165:D165"/>
-    <mergeCell ref="H158:I158"/>
-    <mergeCell ref="H159:I159"/>
-    <mergeCell ref="G160:I160"/>
-    <mergeCell ref="G161:I161"/>
-    <mergeCell ref="H163:I163"/>
-    <mergeCell ref="G165:I165"/>
-    <mergeCell ref="H164:I164"/>
-    <mergeCell ref="B158:D158"/>
-    <mergeCell ref="A160:D160"/>
-    <mergeCell ref="A161:D161"/>
-    <mergeCell ref="A162:D162"/>
-    <mergeCell ref="A163:D163"/>
-    <mergeCell ref="A164:D164"/>
-    <mergeCell ref="A149:D149"/>
-    <mergeCell ref="A150:D150"/>
-    <mergeCell ref="A151:D151"/>
-    <mergeCell ref="A152:D152"/>
-    <mergeCell ref="A153:D153"/>
-    <mergeCell ref="A154:D154"/>
-    <mergeCell ref="G143:I143"/>
-    <mergeCell ref="G142:I142"/>
-    <mergeCell ref="B147:D147"/>
-    <mergeCell ref="A143:D143"/>
-    <mergeCell ref="H137:I137"/>
-    <mergeCell ref="G138:I138"/>
-    <mergeCell ref="G139:I139"/>
-    <mergeCell ref="H141:I141"/>
-    <mergeCell ref="A138:D138"/>
-    <mergeCell ref="A139:D139"/>
-    <mergeCell ref="A140:D140"/>
-    <mergeCell ref="A141:D141"/>
-    <mergeCell ref="A142:D142"/>
+    <mergeCell ref="G99:I99"/>
+    <mergeCell ref="G100:I100"/>
+    <mergeCell ref="G115:I115"/>
     <mergeCell ref="G129:I129"/>
     <mergeCell ref="G130:I130"/>
-    <mergeCell ref="G131:I131"/>
-    <mergeCell ref="G132:I132"/>
-    <mergeCell ref="B136:D136"/>
-    <mergeCell ref="H136:I136"/>
-    <mergeCell ref="A128:D128"/>
-    <mergeCell ref="H121:I121"/>
-    <mergeCell ref="H122:I122"/>
+    <mergeCell ref="G89:I89"/>
+    <mergeCell ref="G134:I134"/>
+    <mergeCell ref="G133:I133"/>
     <mergeCell ref="G123:I123"/>
-    <mergeCell ref="G124:I124"/>
-    <mergeCell ref="H126:I126"/>
-    <mergeCell ref="H127:I127"/>
-    <mergeCell ref="G128:I128"/>
-    <mergeCell ref="B121:D121"/>
-    <mergeCell ref="A123:D123"/>
-    <mergeCell ref="A124:D124"/>
-    <mergeCell ref="A125:D125"/>
-    <mergeCell ref="A126:D126"/>
-    <mergeCell ref="A127:D127"/>
-    <mergeCell ref="A115:D115"/>
-    <mergeCell ref="A116:D116"/>
-    <mergeCell ref="H109:I109"/>
-    <mergeCell ref="H110:I110"/>
-    <mergeCell ref="G111:I111"/>
-    <mergeCell ref="G112:I112"/>
     <mergeCell ref="G114:I114"/>
-    <mergeCell ref="G105:I105"/>
-    <mergeCell ref="B109:D109"/>
-    <mergeCell ref="A111:D111"/>
-    <mergeCell ref="A112:D112"/>
-    <mergeCell ref="A113:D113"/>
-    <mergeCell ref="A114:D114"/>
+    <mergeCell ref="G172:I172"/>
+    <mergeCell ref="G171:I171"/>
+    <mergeCell ref="G170:I170"/>
+    <mergeCell ref="G169:I169"/>
+    <mergeCell ref="G164:I164"/>
+    <mergeCell ref="G157:I157"/>
+    <mergeCell ref="G152:I152"/>
+    <mergeCell ref="G141:I141"/>
+    <mergeCell ref="G146:I146"/>
     <mergeCell ref="H98:I98"/>
-    <mergeCell ref="G99:I99"/>
-    <mergeCell ref="G100:I100"/>
     <mergeCell ref="H102:I102"/>
     <mergeCell ref="H103:I103"/>
-    <mergeCell ref="G104:I104"/>
-    <mergeCell ref="A99:D99"/>
-    <mergeCell ref="A100:D100"/>
-    <mergeCell ref="A101:D101"/>
-    <mergeCell ref="A102:D102"/>
-    <mergeCell ref="A103:D103"/>
-    <mergeCell ref="A104:D104"/>
-    <mergeCell ref="G93:I93"/>
-    <mergeCell ref="G94:I94"/>
-    <mergeCell ref="B97:D97"/>
-    <mergeCell ref="H97:I97"/>
-    <mergeCell ref="A79:D79"/>
-    <mergeCell ref="B86:D86"/>
-    <mergeCell ref="B60:D60"/>
-    <mergeCell ref="B51:D51"/>
-    <mergeCell ref="B37:D37"/>
-    <mergeCell ref="H86:I86"/>
-    <mergeCell ref="H87:I87"/>
-    <mergeCell ref="G88:I88"/>
-    <mergeCell ref="G89:I89"/>
-    <mergeCell ref="H91:I91"/>
-    <mergeCell ref="G65:I65"/>
-    <mergeCell ref="A88:D88"/>
-    <mergeCell ref="A89:D89"/>
-    <mergeCell ref="A90:D90"/>
-    <mergeCell ref="A77:D77"/>
-    <mergeCell ref="A78:D78"/>
-    <mergeCell ref="H92:I92"/>
-    <mergeCell ref="B72:D72"/>
-    <mergeCell ref="A74:D74"/>
-    <mergeCell ref="A75:D75"/>
-    <mergeCell ref="H60:I60"/>
-    <mergeCell ref="H61:I61"/>
-    <mergeCell ref="G62:I62"/>
-    <mergeCell ref="G63:I63"/>
-    <mergeCell ref="G66:I66"/>
-    <mergeCell ref="G57:I57"/>
-    <mergeCell ref="A62:D62"/>
-    <mergeCell ref="A63:D63"/>
-    <mergeCell ref="A64:D64"/>
-    <mergeCell ref="A54:D54"/>
-    <mergeCell ref="A55:D55"/>
-    <mergeCell ref="A56:D56"/>
-    <mergeCell ref="H51:I51"/>
-    <mergeCell ref="H52:I52"/>
-    <mergeCell ref="G53:I53"/>
-    <mergeCell ref="G54:I54"/>
-    <mergeCell ref="G44:I44"/>
-    <mergeCell ref="G45:I45"/>
-    <mergeCell ref="G46:I46"/>
-    <mergeCell ref="G47:I47"/>
-    <mergeCell ref="G48:I48"/>
-    <mergeCell ref="A53:D53"/>
-    <mergeCell ref="G56:I56"/>
+    <mergeCell ref="G119:I119"/>
+    <mergeCell ref="G120:I120"/>
+    <mergeCell ref="G121:I121"/>
+    <mergeCell ref="G122:I122"/>
+    <mergeCell ref="H128:I128"/>
+    <mergeCell ref="H132:I132"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="G10:I10"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="H14:I14"/>
+    <mergeCell ref="H15:I15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="H19:I19"/>
     <mergeCell ref="A41:D41"/>
     <mergeCell ref="A42:D42"/>
     <mergeCell ref="A44:D44"/>
@@ -4757,33 +4455,123 @@
     <mergeCell ref="G27:I27"/>
     <mergeCell ref="G28:I28"/>
     <mergeCell ref="H30:I30"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="A27:D27"/>
-    <mergeCell ref="A28:D28"/>
-    <mergeCell ref="A29:D29"/>
-    <mergeCell ref="A19:D19"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="H14:I14"/>
-    <mergeCell ref="H15:I15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="H19:I19"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="G10:I10"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="A16:D16"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="A5:D5"/>
-    <mergeCell ref="A6:D6"/>
-    <mergeCell ref="A7:D7"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="A54:D54"/>
+    <mergeCell ref="A55:D55"/>
+    <mergeCell ref="A56:D56"/>
+    <mergeCell ref="H51:I51"/>
+    <mergeCell ref="H52:I52"/>
+    <mergeCell ref="G53:I53"/>
+    <mergeCell ref="G54:I54"/>
+    <mergeCell ref="G44:I44"/>
+    <mergeCell ref="G45:I45"/>
+    <mergeCell ref="G46:I46"/>
+    <mergeCell ref="G47:I47"/>
+    <mergeCell ref="G48:I48"/>
+    <mergeCell ref="A53:D53"/>
+    <mergeCell ref="G55:I55"/>
+    <mergeCell ref="H59:I59"/>
+    <mergeCell ref="H60:I60"/>
+    <mergeCell ref="G61:I61"/>
+    <mergeCell ref="G62:I62"/>
+    <mergeCell ref="G64:I64"/>
+    <mergeCell ref="G56:I56"/>
+    <mergeCell ref="A62:D62"/>
+    <mergeCell ref="A63:D63"/>
+    <mergeCell ref="A64:D64"/>
+    <mergeCell ref="B97:D97"/>
+    <mergeCell ref="H97:I97"/>
+    <mergeCell ref="A79:D79"/>
+    <mergeCell ref="B86:D86"/>
+    <mergeCell ref="B60:D60"/>
+    <mergeCell ref="B51:D51"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="H86:I86"/>
+    <mergeCell ref="H87:I87"/>
+    <mergeCell ref="G88:I88"/>
+    <mergeCell ref="H91:I91"/>
+    <mergeCell ref="G63:I63"/>
+    <mergeCell ref="A88:D88"/>
+    <mergeCell ref="A89:D89"/>
+    <mergeCell ref="A90:D90"/>
+    <mergeCell ref="A77:D77"/>
+    <mergeCell ref="A78:D78"/>
+    <mergeCell ref="H92:I92"/>
+    <mergeCell ref="B72:D72"/>
+    <mergeCell ref="A74:D74"/>
+    <mergeCell ref="A75:D75"/>
+    <mergeCell ref="H78:I78"/>
+    <mergeCell ref="A76:D76"/>
+    <mergeCell ref="H72:I72"/>
+    <mergeCell ref="A99:D99"/>
+    <mergeCell ref="A100:D100"/>
+    <mergeCell ref="A101:D101"/>
+    <mergeCell ref="A102:D102"/>
+    <mergeCell ref="A103:D103"/>
+    <mergeCell ref="A104:D104"/>
+    <mergeCell ref="B127:D127"/>
+    <mergeCell ref="H127:I127"/>
+    <mergeCell ref="A119:D119"/>
+    <mergeCell ref="H112:I112"/>
+    <mergeCell ref="H113:I113"/>
+    <mergeCell ref="H117:I117"/>
+    <mergeCell ref="H118:I118"/>
+    <mergeCell ref="B112:D112"/>
+    <mergeCell ref="A114:D114"/>
+    <mergeCell ref="A115:D115"/>
+    <mergeCell ref="A116:D116"/>
+    <mergeCell ref="A117:D117"/>
+    <mergeCell ref="A118:D118"/>
+    <mergeCell ref="A129:D129"/>
+    <mergeCell ref="A130:D130"/>
+    <mergeCell ref="A131:D131"/>
+    <mergeCell ref="A132:D132"/>
+    <mergeCell ref="A133:D133"/>
+    <mergeCell ref="A134:D134"/>
+    <mergeCell ref="H138:I138"/>
+    <mergeCell ref="H139:I139"/>
+    <mergeCell ref="G140:I140"/>
+    <mergeCell ref="H143:I143"/>
+    <mergeCell ref="H144:I144"/>
+    <mergeCell ref="B138:D138"/>
+    <mergeCell ref="A140:D140"/>
+    <mergeCell ref="A141:D141"/>
+    <mergeCell ref="A142:D142"/>
+    <mergeCell ref="A143:D143"/>
+    <mergeCell ref="A144:D144"/>
+    <mergeCell ref="A156:D156"/>
+    <mergeCell ref="H149:I149"/>
+    <mergeCell ref="H150:I150"/>
+    <mergeCell ref="G151:I151"/>
+    <mergeCell ref="H154:I154"/>
+    <mergeCell ref="G145:I145"/>
+    <mergeCell ref="B149:D149"/>
+    <mergeCell ref="A151:D151"/>
+    <mergeCell ref="A145:D145"/>
+    <mergeCell ref="H155:I155"/>
+    <mergeCell ref="H73:I73"/>
+    <mergeCell ref="H77:I77"/>
+    <mergeCell ref="G93:I93"/>
+    <mergeCell ref="G94:I94"/>
+    <mergeCell ref="G105:I105"/>
+    <mergeCell ref="G104:I104"/>
+    <mergeCell ref="H167:I167"/>
+    <mergeCell ref="G168:I168"/>
+    <mergeCell ref="B161:D161"/>
+    <mergeCell ref="A163:D163"/>
+    <mergeCell ref="A164:D164"/>
+    <mergeCell ref="A165:D165"/>
+    <mergeCell ref="A166:D166"/>
+    <mergeCell ref="A167:D167"/>
+    <mergeCell ref="A168:D168"/>
+    <mergeCell ref="H161:I161"/>
+    <mergeCell ref="G156:I156"/>
+    <mergeCell ref="H162:I162"/>
+    <mergeCell ref="G163:I163"/>
+    <mergeCell ref="H166:I166"/>
+    <mergeCell ref="A152:D152"/>
+    <mergeCell ref="A153:D153"/>
+    <mergeCell ref="A154:D154"/>
+    <mergeCell ref="A155:D155"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
